--- a/data/yield_data.xlsx
+++ b/data/yield_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18560" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19153" uniqueCount="961">
   <si>
     <t>Date</t>
   </si>
@@ -2721,40 +2721,7 @@
     <t>2026/27</t>
   </si>
   <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>MHG6058</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>KK9686</t>
-  </si>
-  <si>
     <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>DG14000</t>
   </si>
   <si>
     <t>A12001</t>
@@ -2767,6 +2734,9 @@
   </si>
   <si>
     <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>2026-05-16</t>
@@ -2784,7 +2754,22 @@
     <t>2026-05-21</t>
   </si>
   <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
     <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>MHG6058</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
   </si>
   <si>
     <t>2026-05-30</t>
@@ -2793,16 +2778,22 @@
     <t>2026-05-31</t>
   </si>
   <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
     <t>2026-06-03</t>
   </si>
   <si>
+    <t>XXX</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
-    <t>XXX</t>
+    <t>2026-06-05</t>
   </si>
   <si>
     <t>2026-06-06</t>
@@ -2820,7 +2811,13 @@
     <t>2026-06-10</t>
   </si>
   <si>
+    <t>KK9686</t>
+  </si>
+  <si>
     <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
   </si>
   <si>
     <t>2026-06-13</t>
@@ -2857,6 +2854,54 @@
   </si>
   <si>
     <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>AR008</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>AE002</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>53.08</t>
+  </si>
+  <si>
+    <t>336721</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
   </si>
 </sst>
 </file>
@@ -3219,10 +3264,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3996"/>
+  <dimension ref="A1:H4114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -84625,16 +84672,16 @@
     </row>
     <row r="3464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3464" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3464" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3464" t="s">
         <v>138</v>
       </c>
       <c r="D3464">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3464">
         <v>30.3</v>
@@ -84651,22 +84698,22 @@
     </row>
     <row r="3465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3465" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3465" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3465" t="s">
         <v>138</v>
       </c>
       <c r="D3465">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3465">
         <v>27.92</v>
       </c>
       <c r="F3465" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="G3465">
         <v>396452</v>
@@ -84677,16 +84724,16 @@
     </row>
     <row r="3466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3466" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3466" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3466" t="s">
         <v>138</v>
       </c>
       <c r="D3466">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3466">
         <v>29.36</v>
@@ -84703,16 +84750,16 @@
     </row>
     <row r="3467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3467" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3467" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3467" t="s">
         <v>138</v>
       </c>
       <c r="D3467">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3467">
         <v>24.9</v>
@@ -84729,16 +84776,16 @@
     </row>
     <row r="3468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3468" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3468" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3468" t="s">
         <v>138</v>
       </c>
       <c r="D3468">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3468">
         <v>23.16</v>
@@ -84755,16 +84802,16 @@
     </row>
     <row r="3469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3469" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3469" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3469" t="s">
         <v>138</v>
       </c>
       <c r="D3469">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3469">
         <v>27.14</v>
@@ -84781,16 +84828,16 @@
     </row>
     <row r="3470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3470" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3470" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3470" t="s">
         <v>138</v>
       </c>
       <c r="D3470">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3470">
         <v>28.36</v>
@@ -84807,16 +84854,16 @@
     </row>
     <row r="3471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3471" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3471" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3471" t="s">
         <v>138</v>
       </c>
       <c r="D3471">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3471">
         <v>24.98</v>
@@ -84833,16 +84880,16 @@
     </row>
     <row r="3472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3472" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3472" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3472" t="s">
         <v>138</v>
       </c>
       <c r="D3472">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3472">
         <v>25.28</v>
@@ -84859,16 +84906,16 @@
     </row>
     <row r="3473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3473" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3473" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3473" t="s">
         <v>138</v>
       </c>
       <c r="D3473">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3473">
         <v>30.88</v>
@@ -84885,16 +84932,16 @@
     </row>
     <row r="3474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3474" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3474" t="s">
-        <v>911</v>
+        <v>159</v>
       </c>
       <c r="C3474" t="s">
         <v>138</v>
       </c>
       <c r="D3474">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3474">
         <v>27.44</v>
@@ -84911,16 +84958,16 @@
     </row>
     <row r="3475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3475" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3475" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3475" t="s">
         <v>138</v>
       </c>
       <c r="D3475">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3475">
         <v>30.14</v>
@@ -84937,16 +84984,16 @@
     </row>
     <row r="3476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3476" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3476" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3476" t="s">
         <v>138</v>
       </c>
       <c r="D3476">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3476">
         <v>26.6</v>
@@ -84963,16 +85010,16 @@
     </row>
     <row r="3477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3477" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3477" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3477" t="s">
         <v>138</v>
       </c>
       <c r="D3477">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3477">
         <v>32.82</v>
@@ -84989,16 +85036,16 @@
     </row>
     <row r="3478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3478" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3478" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3478" t="s">
         <v>138</v>
       </c>
       <c r="D3478">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3478">
         <v>31.94</v>
@@ -85015,22 +85062,22 @@
     </row>
     <row r="3479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3479" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3479" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3479" t="s">
         <v>138</v>
       </c>
       <c r="D3479">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3479">
         <v>30.9</v>
       </c>
       <c r="F3479" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3479">
         <v>396466</v>
@@ -85041,16 +85088,16 @@
     </row>
     <row r="3480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3480" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3480" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3480" t="s">
         <v>138</v>
       </c>
       <c r="D3480">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3480">
         <v>24.04</v>
@@ -85067,10 +85114,10 @@
     </row>
     <row r="3481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3481" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3481" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3481" t="s">
         <v>138</v>
@@ -85093,10 +85140,10 @@
     </row>
     <row r="3482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3482" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3482" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3482" t="s">
         <v>138</v>
@@ -85119,16 +85166,16 @@
     </row>
     <row r="3483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3483" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3483" t="s">
-        <v>911</v>
+        <v>158</v>
       </c>
       <c r="C3483" t="s">
         <v>138</v>
       </c>
       <c r="D3483">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3483">
         <v>25.56</v>
@@ -85145,16 +85192,16 @@
     </row>
     <row r="3484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3484" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3484" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3484" t="s">
         <v>138</v>
       </c>
       <c r="D3484">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3484">
         <v>26.22</v>
@@ -85171,10 +85218,10 @@
     </row>
     <row r="3485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3485" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3485" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3485" t="s">
         <v>138</v>
@@ -85197,10 +85244,10 @@
     </row>
     <row r="3486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3486" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3486" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3486" t="s">
         <v>138</v>
@@ -85223,16 +85270,16 @@
     </row>
     <row r="3487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3487" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3487" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3487" t="s">
         <v>138</v>
       </c>
       <c r="D3487">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3487">
         <v>23.8</v>
@@ -85249,22 +85296,22 @@
     </row>
     <row r="3488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3488" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B3488" t="s">
-        <v>911</v>
+        <v>157</v>
       </c>
       <c r="C3488" t="s">
         <v>138</v>
       </c>
       <c r="D3488">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3488">
         <v>28.34</v>
       </c>
       <c r="F3488" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3488">
         <v>396475</v>
@@ -85275,7 +85322,7 @@
     </row>
     <row r="3489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3489" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3489" t="s">
         <v>337</v>
@@ -85301,7 +85348,7 @@
     </row>
     <row r="3490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3490" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3490" t="s">
         <v>335</v>
@@ -85327,7 +85374,7 @@
     </row>
     <row r="3491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3491" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3491" t="s">
         <v>334</v>
@@ -85353,7 +85400,7 @@
     </row>
     <row r="3492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3492" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3492" t="s">
         <v>155</v>
@@ -85362,7 +85409,7 @@
         <v>138</v>
       </c>
       <c r="D3492">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3492">
         <v>35.22</v>
@@ -85379,7 +85426,7 @@
     </row>
     <row r="3493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3493" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3493" t="s">
         <v>155</v>
@@ -85388,7 +85435,7 @@
         <v>138</v>
       </c>
       <c r="D3493">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3493">
         <v>29.76</v>
@@ -85405,7 +85452,7 @@
     </row>
     <row r="3494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3494" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3494" t="s">
         <v>155</v>
@@ -85414,7 +85461,7 @@
         <v>138</v>
       </c>
       <c r="D3494">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3494">
         <v>33.799999999999997</v>
@@ -85431,7 +85478,7 @@
     </row>
     <row r="3495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3495" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3495" t="s">
         <v>155</v>
@@ -85440,7 +85487,7 @@
         <v>138</v>
       </c>
       <c r="D3495">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3495">
         <v>25.46</v>
@@ -85457,7 +85504,7 @@
     </row>
     <row r="3496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3496" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3496" t="s">
         <v>155</v>
@@ -85466,7 +85513,7 @@
         <v>138</v>
       </c>
       <c r="D3496">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3496">
         <v>28.86</v>
@@ -85483,7 +85530,7 @@
     </row>
     <row r="3497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3497" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3497" t="s">
         <v>155</v>
@@ -85492,7 +85539,7 @@
         <v>138</v>
       </c>
       <c r="D3497">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3497">
         <v>29.12</v>
@@ -85509,7 +85556,7 @@
     </row>
     <row r="3498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3498" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3498" t="s">
         <v>155</v>
@@ -85518,7 +85565,7 @@
         <v>138</v>
       </c>
       <c r="D3498">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3498">
         <v>29.32</v>
@@ -85535,7 +85582,7 @@
     </row>
     <row r="3499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3499" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3499" t="s">
         <v>155</v>
@@ -85544,7 +85591,7 @@
         <v>138</v>
       </c>
       <c r="D3499">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3499">
         <v>15.85</v>
@@ -85561,7 +85608,7 @@
     </row>
     <row r="3500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3500" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3500" t="s">
         <v>155</v>
@@ -85570,7 +85617,7 @@
         <v>138</v>
       </c>
       <c r="D3500">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3500">
         <v>32.32</v>
@@ -85587,7 +85634,7 @@
     </row>
     <row r="3501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3501" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3501" t="s">
         <v>155</v>
@@ -85596,7 +85643,7 @@
         <v>138</v>
       </c>
       <c r="D3501">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3501">
         <v>32</v>
@@ -85613,7 +85660,7 @@
     </row>
     <row r="3502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3502" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3502" t="s">
         <v>156</v>
@@ -85639,7 +85686,7 @@
     </row>
     <row r="3503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3503" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3503" t="s">
         <v>156</v>
@@ -85665,7 +85712,7 @@
     </row>
     <row r="3504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3504" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3504" t="s">
         <v>156</v>
@@ -85674,7 +85721,7 @@
         <v>138</v>
       </c>
       <c r="D3504">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3504">
         <v>33.76</v>
@@ -85691,7 +85738,7 @@
     </row>
     <row r="3505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3505" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3505" t="s">
         <v>156</v>
@@ -85717,7 +85764,7 @@
     </row>
     <row r="3506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3506" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3506" t="s">
         <v>156</v>
@@ -85726,7 +85773,7 @@
         <v>138</v>
       </c>
       <c r="D3506">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3506">
         <v>33.14</v>
@@ -85743,7 +85790,7 @@
     </row>
     <row r="3507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3507" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3507" t="s">
         <v>156</v>
@@ -85769,7 +85816,7 @@
     </row>
     <row r="3508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3508" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3508" t="s">
         <v>156</v>
@@ -85778,7 +85825,7 @@
         <v>138</v>
       </c>
       <c r="D3508">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E3508">
         <v>25.88</v>
@@ -85795,7 +85842,7 @@
     </row>
     <row r="3509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3509" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3509" t="s">
         <v>156</v>
@@ -85804,7 +85851,7 @@
         <v>138</v>
       </c>
       <c r="D3509">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3509">
         <v>31.42</v>
@@ -85821,7 +85868,7 @@
     </row>
     <row r="3510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3510" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3510" t="s">
         <v>156</v>
@@ -85830,7 +85877,7 @@
         <v>138</v>
       </c>
       <c r="D3510">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3510">
         <v>34.96</v>
@@ -85847,7 +85894,7 @@
     </row>
     <row r="3511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3511" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3511" t="s">
         <v>156</v>
@@ -85856,7 +85903,7 @@
         <v>138</v>
       </c>
       <c r="D3511">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3511">
         <v>31.44</v>
@@ -85873,7 +85920,7 @@
     </row>
     <row r="3512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3512" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3512" t="s">
         <v>156</v>
@@ -85899,7 +85946,7 @@
     </row>
     <row r="3513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3513" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3513" t="s">
         <v>157</v>
@@ -85925,7 +85972,7 @@
     </row>
     <row r="3514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3514" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3514" t="s">
         <v>157</v>
@@ -85951,7 +85998,7 @@
     </row>
     <row r="3515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3515" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3515" t="s">
         <v>157</v>
@@ -85960,7 +86007,7 @@
         <v>138</v>
       </c>
       <c r="D3515">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3515">
         <v>29.68</v>
@@ -85977,7 +86024,7 @@
     </row>
     <row r="3516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3516" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B3516" t="s">
         <v>157</v>
@@ -85986,7 +86033,7 @@
         <v>138</v>
       </c>
       <c r="D3516">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3516">
         <v>23.1</v>
@@ -86003,7 +86050,7 @@
     </row>
     <row r="3517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3517" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="B3517" t="s">
         <v>338</v>
@@ -86029,7 +86076,7 @@
     </row>
     <row r="3518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3518" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="B3518" t="s">
         <v>337</v>
@@ -86055,7 +86102,7 @@
     </row>
     <row r="3519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3519" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3519" t="s">
         <v>344</v>
@@ -86081,7 +86128,7 @@
     </row>
     <row r="3520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3520" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3520" t="s">
         <v>344</v>
@@ -86107,7 +86154,7 @@
     </row>
     <row r="3521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3521" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3521" t="s">
         <v>344</v>
@@ -86133,7 +86180,7 @@
     </row>
     <row r="3522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3522" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3522" t="s">
         <v>344</v>
@@ -86159,7 +86206,7 @@
     </row>
     <row r="3523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3523" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3523" t="s">
         <v>344</v>
@@ -86185,7 +86232,7 @@
     </row>
     <row r="3524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3524" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3524" t="s">
         <v>344</v>
@@ -86211,7 +86258,7 @@
     </row>
     <row r="3525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3525" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3525" t="s">
         <v>344</v>
@@ -86237,7 +86284,7 @@
     </row>
     <row r="3526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3526" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3526" t="s">
         <v>344</v>
@@ -86263,7 +86310,7 @@
     </row>
     <row r="3527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3527" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3527" t="s">
         <v>343</v>
@@ -86289,7 +86336,7 @@
     </row>
     <row r="3528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3528" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B3528" t="s">
         <v>343</v>
@@ -86315,7 +86362,7 @@
     </row>
     <row r="3529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3529" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3529" t="s">
         <v>343</v>
@@ -86341,7 +86388,7 @@
     </row>
     <row r="3530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3530" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3530" t="s">
         <v>343</v>
@@ -86367,7 +86414,7 @@
     </row>
     <row r="3531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3531" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3531" t="s">
         <v>343</v>
@@ -86393,7 +86440,7 @@
     </row>
     <row r="3532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3532" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3532" t="s">
         <v>343</v>
@@ -86408,7 +86455,7 @@
         <v>28.2</v>
       </c>
       <c r="F3532" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3532">
         <v>397118</v>
@@ -86419,7 +86466,7 @@
     </row>
     <row r="3533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3533" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3533" t="s">
         <v>343</v>
@@ -86445,7 +86492,7 @@
     </row>
     <row r="3534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3534" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3534" t="s">
         <v>343</v>
@@ -86471,7 +86518,7 @@
     </row>
     <row r="3535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3535" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3535" t="s">
         <v>343</v>
@@ -86497,7 +86544,7 @@
     </row>
     <row r="3536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3536" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3536" t="s">
         <v>343</v>
@@ -86523,7 +86570,7 @@
     </row>
     <row r="3537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3537" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3537" t="s">
         <v>343</v>
@@ -86549,7 +86596,7 @@
     </row>
     <row r="3538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3538" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3538" t="s">
         <v>343</v>
@@ -86564,7 +86611,7 @@
         <v>35.619999999999997</v>
       </c>
       <c r="F3538" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3538">
         <v>397124</v>
@@ -86575,7 +86622,7 @@
     </row>
     <row r="3539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3539" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3539" t="s">
         <v>343</v>
@@ -86601,7 +86648,7 @@
     </row>
     <row r="3540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3540" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3540" t="s">
         <v>342</v>
@@ -86627,7 +86674,7 @@
     </row>
     <row r="3541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3541" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3541" t="s">
         <v>342</v>
@@ -86642,7 +86689,7 @@
         <v>34.479999999999997</v>
       </c>
       <c r="F3541" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3541">
         <v>397127</v>
@@ -86653,7 +86700,7 @@
     </row>
     <row r="3542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3542" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3542" t="s">
         <v>342</v>
@@ -86679,7 +86726,7 @@
     </row>
     <row r="3543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3543" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3543" t="s">
         <v>342</v>
@@ -86705,7 +86752,7 @@
     </row>
     <row r="3544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3544" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3544" t="s">
         <v>342</v>
@@ -86731,7 +86778,7 @@
     </row>
     <row r="3545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3545" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3545" t="s">
         <v>342</v>
@@ -86757,7 +86804,7 @@
     </row>
     <row r="3546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3546" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3546" t="s">
         <v>342</v>
@@ -86783,7 +86830,7 @@
     </row>
     <row r="3547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3547" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3547" t="s">
         <v>342</v>
@@ -86809,7 +86856,7 @@
     </row>
     <row r="3548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3548" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3548" t="s">
         <v>342</v>
@@ -86824,7 +86871,7 @@
         <v>38.159999999999997</v>
       </c>
       <c r="F3548" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3548">
         <v>397136</v>
@@ -86835,7 +86882,7 @@
     </row>
     <row r="3549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3549" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3549" t="s">
         <v>342</v>
@@ -86861,7 +86908,7 @@
     </row>
     <row r="3550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3550" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3550" t="s">
         <v>342</v>
@@ -86876,7 +86923,7 @@
         <v>29.22</v>
       </c>
       <c r="F3550" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3550">
         <v>397139</v>
@@ -86887,7 +86934,7 @@
     </row>
     <row r="3551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3551" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3551" t="s">
         <v>341</v>
@@ -86913,7 +86960,7 @@
     </row>
     <row r="3552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3552" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3552" t="s">
         <v>341</v>
@@ -86939,7 +86986,7 @@
     </row>
     <row r="3553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3553" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3553" t="s">
         <v>341</v>
@@ -86965,7 +87012,7 @@
     </row>
     <row r="3554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3554" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3554" t="s">
         <v>341</v>
@@ -86991,7 +87038,7 @@
     </row>
     <row r="3555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3555" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3555" t="s">
         <v>341</v>
@@ -87017,7 +87064,7 @@
     </row>
     <row r="3556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3556" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3556" t="s">
         <v>341</v>
@@ -87043,7 +87090,7 @@
     </row>
     <row r="3557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3557" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3557" t="s">
         <v>341</v>
@@ -87069,7 +87116,7 @@
     </row>
     <row r="3558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3558" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3558" t="s">
         <v>341</v>
@@ -87084,7 +87131,7 @@
         <v>31.38</v>
       </c>
       <c r="F3558" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3558">
         <v>397147</v>
@@ -87095,7 +87142,7 @@
     </row>
     <row r="3559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3559" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3559" t="s">
         <v>341</v>
@@ -87121,7 +87168,7 @@
     </row>
     <row r="3560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3560" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3560" t="s">
         <v>341</v>
@@ -87147,7 +87194,7 @@
     </row>
     <row r="3561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3561" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3561" t="s">
         <v>341</v>
@@ -87173,7 +87220,7 @@
     </row>
     <row r="3562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3562" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B3562" t="s">
         <v>341</v>
@@ -87199,10 +87246,10 @@
     </row>
     <row r="3563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3563" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B3563" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C3563" t="s">
         <v>138</v>
@@ -87225,16 +87272,16 @@
     </row>
     <row r="3564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3564" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B3564" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3564" t="s">
         <v>138</v>
       </c>
       <c r="D3564">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3564">
         <v>11.3</v>
@@ -87251,7 +87298,7 @@
     </row>
     <row r="3565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3565" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B3565" t="s">
         <v>157</v>
@@ -87277,16 +87324,16 @@
     </row>
     <row r="3566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3566" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B3566" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3566" t="s">
         <v>138</v>
       </c>
       <c r="D3566">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3566">
         <v>12.88</v>
@@ -87303,7 +87350,7 @@
     </row>
     <row r="3567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3567" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B3567" t="s">
         <v>344</v>
@@ -87329,7 +87376,7 @@
     </row>
     <row r="3568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3568" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="B3568" t="s">
         <v>342</v>
@@ -87355,7 +87402,7 @@
     </row>
     <row r="3569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3569" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="B3569" t="s">
         <v>344</v>
@@ -87381,7 +87428,7 @@
     </row>
     <row r="3570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3570" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3570" t="s">
         <v>180</v>
@@ -87407,7 +87454,7 @@
     </row>
     <row r="3571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3571" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3571" t="s">
         <v>180</v>
@@ -87433,7 +87480,7 @@
     </row>
     <row r="3572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3572" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3572" t="s">
         <v>179</v>
@@ -87459,7 +87506,7 @@
     </row>
     <row r="3573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3573" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3573" t="s">
         <v>179</v>
@@ -87474,7 +87521,7 @@
         <v>39.619999999999997</v>
       </c>
       <c r="F3573" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3573">
         <v>397510</v>
@@ -87485,7 +87532,7 @@
     </row>
     <row r="3574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3574" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3574" t="s">
         <v>179</v>
@@ -87511,7 +87558,7 @@
     </row>
     <row r="3575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3575" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3575" t="s">
         <v>179</v>
@@ -87537,7 +87584,7 @@
     </row>
     <row r="3576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3576" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3576" t="s">
         <v>179</v>
@@ -87563,7 +87610,7 @@
     </row>
     <row r="3577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3577" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3577" t="s">
         <v>179</v>
@@ -87589,7 +87636,7 @@
     </row>
     <row r="3578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3578" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3578" t="s">
         <v>179</v>
@@ -87615,7 +87662,7 @@
     </row>
     <row r="3579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3579" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3579" t="s">
         <v>178</v>
@@ -87641,7 +87688,7 @@
     </row>
     <row r="3580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3580" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3580" t="s">
         <v>178</v>
@@ -87667,7 +87714,7 @@
     </row>
     <row r="3581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3581" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3581" t="s">
         <v>178</v>
@@ -87693,7 +87740,7 @@
     </row>
     <row r="3582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3582" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3582" t="s">
         <v>178</v>
@@ -87708,7 +87755,7 @@
         <v>30.12</v>
       </c>
       <c r="F3582" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3582">
         <v>397506</v>
@@ -87719,7 +87766,7 @@
     </row>
     <row r="3583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3583" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3583" t="s">
         <v>178</v>
@@ -87745,7 +87792,7 @@
     </row>
     <row r="3584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3584" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B3584" t="s">
         <v>178</v>
@@ -87771,7 +87818,7 @@
     </row>
     <row r="3585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3585" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3585" t="s">
         <v>180</v>
@@ -87797,7 +87844,7 @@
     </row>
     <row r="3586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3586" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3586" t="s">
         <v>180</v>
@@ -87823,7 +87870,7 @@
     </row>
     <row r="3587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3587" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3587" t="s">
         <v>180</v>
@@ -87849,7 +87896,7 @@
     </row>
     <row r="3588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3588" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3588" t="s">
         <v>180</v>
@@ -87875,7 +87922,7 @@
     </row>
     <row r="3589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3589" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3589" t="s">
         <v>180</v>
@@ -87901,7 +87948,7 @@
     </row>
     <row r="3590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3590" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3590" t="s">
         <v>180</v>
@@ -87927,7 +87974,7 @@
     </row>
     <row r="3591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3591" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3591" t="s">
         <v>282</v>
@@ -87953,7 +88000,7 @@
     </row>
     <row r="3592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3592" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3592" t="s">
         <v>282</v>
@@ -87979,7 +88026,7 @@
     </row>
     <row r="3593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3593" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3593" t="s">
         <v>282</v>
@@ -88005,7 +88052,7 @@
     </row>
     <row r="3594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3594" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3594" t="s">
         <v>281</v>
@@ -88031,7 +88078,7 @@
     </row>
     <row r="3595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3595" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3595" t="s">
         <v>281</v>
@@ -88057,7 +88104,7 @@
     </row>
     <row r="3596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3596" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3596" t="s">
         <v>281</v>
@@ -88083,7 +88130,7 @@
     </row>
     <row r="3597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3597" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3597" t="s">
         <v>281</v>
@@ -88109,7 +88156,7 @@
     </row>
     <row r="3598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3598" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3598" t="s">
         <v>281</v>
@@ -88135,7 +88182,7 @@
     </row>
     <row r="3599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3599" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3599" t="s">
         <v>281</v>
@@ -88161,7 +88208,7 @@
     </row>
     <row r="3600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3600" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3600" t="s">
         <v>281</v>
@@ -88187,7 +88234,7 @@
     </row>
     <row r="3601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3601" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3601" t="s">
         <v>281</v>
@@ -88213,7 +88260,7 @@
     </row>
     <row r="3602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3602" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3602" t="s">
         <v>281</v>
@@ -88239,7 +88286,7 @@
     </row>
     <row r="3603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3603" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3603" t="s">
         <v>281</v>
@@ -88265,7 +88312,7 @@
     </row>
     <row r="3604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3604" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3604" t="s">
         <v>280</v>
@@ -88291,7 +88338,7 @@
     </row>
     <row r="3605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3605" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3605" t="s">
         <v>281</v>
@@ -88317,7 +88364,7 @@
     </row>
     <row r="3606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3606" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3606" t="s">
         <v>280</v>
@@ -88343,7 +88390,7 @@
     </row>
     <row r="3607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3607" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3607" t="s">
         <v>280</v>
@@ -88369,7 +88416,7 @@
     </row>
     <row r="3608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3608" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B3608" t="s">
         <v>280</v>
@@ -88395,7 +88442,7 @@
     </row>
     <row r="3609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3609" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3609" t="s">
         <v>280</v>
@@ -88421,7 +88468,7 @@
     </row>
     <row r="3610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3610" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3610" t="s">
         <v>280</v>
@@ -88447,7 +88494,7 @@
     </row>
     <row r="3611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3611" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3611" t="s">
         <v>280</v>
@@ -88473,7 +88520,7 @@
     </row>
     <row r="3612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3612" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3612" t="s">
         <v>280</v>
@@ -88499,7 +88546,7 @@
     </row>
     <row r="3613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3613" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3613" t="s">
         <v>280</v>
@@ -88525,7 +88572,7 @@
     </row>
     <row r="3614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3614" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3614" t="s">
         <v>280</v>
@@ -88551,7 +88598,7 @@
     </row>
     <row r="3615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3615" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3615" t="s">
         <v>280</v>
@@ -88577,7 +88624,7 @@
     </row>
     <row r="3616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3616" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3616" t="s">
         <v>279</v>
@@ -88603,7 +88650,7 @@
     </row>
     <row r="3617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3617" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3617" t="s">
         <v>279</v>
@@ -88629,7 +88676,7 @@
     </row>
     <row r="3618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3618" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3618" t="s">
         <v>279</v>
@@ -88655,7 +88702,7 @@
     </row>
     <row r="3619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3619" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3619" t="s">
         <v>279</v>
@@ -88681,7 +88728,7 @@
     </row>
     <row r="3620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3620" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3620" t="s">
         <v>279</v>
@@ -88707,7 +88754,7 @@
     </row>
     <row r="3621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3621" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3621" t="s">
         <v>279</v>
@@ -88733,7 +88780,7 @@
     </row>
     <row r="3622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3622" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3622" t="s">
         <v>279</v>
@@ -88759,7 +88806,7 @@
     </row>
     <row r="3623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3623" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3623" t="s">
         <v>279</v>
@@ -88785,7 +88832,7 @@
     </row>
     <row r="3624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3624" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B3624" t="s">
         <v>279</v>
@@ -88811,7 +88858,7 @@
     </row>
     <row r="3625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3625" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3625" t="s">
         <v>65</v>
@@ -88837,7 +88884,7 @@
     </row>
     <row r="3626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3626" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3626" t="s">
         <v>65</v>
@@ -88863,7 +88910,7 @@
     </row>
     <row r="3627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3627" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3627" t="s">
         <v>65</v>
@@ -88889,7 +88936,7 @@
     </row>
     <row r="3628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3628" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3628" t="s">
         <v>65</v>
@@ -88915,7 +88962,7 @@
     </row>
     <row r="3629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3629" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3629" t="s">
         <v>65</v>
@@ -88941,7 +88988,7 @@
     </row>
     <row r="3630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3630" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3630" t="s">
         <v>66</v>
@@ -88967,7 +89014,7 @@
     </row>
     <row r="3631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3631" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3631" t="s">
         <v>65</v>
@@ -88993,7 +89040,7 @@
     </row>
     <row r="3632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3632" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3632" t="s">
         <v>66</v>
@@ -89019,7 +89066,7 @@
     </row>
     <row r="3633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3633" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3633" t="s">
         <v>66</v>
@@ -89045,7 +89092,7 @@
     </row>
     <row r="3634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3634" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3634" t="s">
         <v>66</v>
@@ -89071,7 +89118,7 @@
     </row>
     <row r="3635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3635" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3635" t="s">
         <v>66</v>
@@ -89097,7 +89144,7 @@
     </row>
     <row r="3636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3636" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3636" t="s">
         <v>66</v>
@@ -89123,7 +89170,7 @@
     </row>
     <row r="3637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3637" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3637" t="s">
         <v>66</v>
@@ -89149,7 +89196,7 @@
     </row>
     <row r="3638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3638" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3638" t="s">
         <v>67</v>
@@ -89175,7 +89222,7 @@
     </row>
     <row r="3639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3639" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3639" t="s">
         <v>67</v>
@@ -89201,7 +89248,7 @@
     </row>
     <row r="3640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3640" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3640" t="s">
         <v>67</v>
@@ -89227,7 +89274,7 @@
     </row>
     <row r="3641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3641" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3641" t="s">
         <v>65</v>
@@ -89253,7 +89300,7 @@
     </row>
     <row r="3642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3642" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3642" t="s">
         <v>67</v>
@@ -89279,7 +89326,7 @@
     </row>
     <row r="3643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3643" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3643" t="s">
         <v>67</v>
@@ -89305,7 +89352,7 @@
     </row>
     <row r="3644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3644" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3644" t="s">
         <v>67</v>
@@ -89331,7 +89378,7 @@
     </row>
     <row r="3645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3645" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3645" t="s">
         <v>68</v>
@@ -89357,7 +89404,7 @@
     </row>
     <row r="3646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3646" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3646" t="s">
         <v>67</v>
@@ -89383,7 +89430,7 @@
     </row>
     <row r="3647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3647" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3647" t="s">
         <v>68</v>
@@ -89409,7 +89456,7 @@
     </row>
     <row r="3648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3648" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3648" t="s">
         <v>179</v>
@@ -89435,7 +89482,7 @@
     </row>
     <row r="3649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3649" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3649" t="s">
         <v>68</v>
@@ -89461,7 +89508,7 @@
     </row>
     <row r="3650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3650" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3650" t="s">
         <v>68</v>
@@ -89487,7 +89534,7 @@
     </row>
     <row r="3651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3651" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3651" t="s">
         <v>178</v>
@@ -89513,7 +89560,7 @@
     </row>
     <row r="3652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3652" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3652" t="s">
         <v>68</v>
@@ -89539,7 +89586,7 @@
     </row>
     <row r="3653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3653" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3653" t="s">
         <v>69</v>
@@ -89565,7 +89612,7 @@
     </row>
     <row r="3654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3654" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3654" t="s">
         <v>69</v>
@@ -89591,7 +89638,7 @@
     </row>
     <row r="3655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3655" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3655" t="s">
         <v>69</v>
@@ -89617,7 +89664,7 @@
     </row>
     <row r="3656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3656" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3656" t="s">
         <v>69</v>
@@ -89643,7 +89690,7 @@
     </row>
     <row r="3657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3657" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3657" t="s">
         <v>279</v>
@@ -89669,7 +89716,7 @@
     </row>
     <row r="3658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3658" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3658" t="s">
         <v>68</v>
@@ -89695,7 +89742,7 @@
     </row>
     <row r="3659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3659" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3659" t="s">
         <v>69</v>
@@ -89721,7 +89768,7 @@
     </row>
     <row r="3660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3660" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3660" t="s">
         <v>69</v>
@@ -89747,7 +89794,7 @@
     </row>
     <row r="3661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3661" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3661" t="s">
         <v>280</v>
@@ -89773,7 +89820,7 @@
     </row>
     <row r="3662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3662" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3662" t="s">
         <v>281</v>
@@ -89799,7 +89846,7 @@
     </row>
     <row r="3663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3663" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3663" t="s">
         <v>70</v>
@@ -89825,7 +89872,7 @@
     </row>
     <row r="3664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3664" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3664" t="s">
         <v>70</v>
@@ -89851,7 +89898,7 @@
     </row>
     <row r="3665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3665" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3665" t="s">
         <v>70</v>
@@ -89877,7 +89924,7 @@
     </row>
     <row r="3666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3666" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3666" t="s">
         <v>70</v>
@@ -89903,7 +89950,7 @@
     </row>
     <row r="3667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3667" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3667" t="s">
         <v>70</v>
@@ -89929,7 +89976,7 @@
     </row>
     <row r="3668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3668" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3668" t="s">
         <v>70</v>
@@ -89955,7 +90002,7 @@
     </row>
     <row r="3669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3669" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3669" t="s">
         <v>71</v>
@@ -89981,7 +90028,7 @@
     </row>
     <row r="3670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3670" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3670" t="s">
         <v>71</v>
@@ -90007,7 +90054,7 @@
     </row>
     <row r="3671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3671" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3671" t="s">
         <v>71</v>
@@ -90033,7 +90080,7 @@
     </row>
     <row r="3672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3672" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3672" t="s">
         <v>71</v>
@@ -90059,7 +90106,7 @@
     </row>
     <row r="3673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3673" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3673" t="s">
         <v>71</v>
@@ -90085,7 +90132,7 @@
     </row>
     <row r="3674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3674" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3674" t="s">
         <v>71</v>
@@ -90111,7 +90158,7 @@
     </row>
     <row r="3675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3675" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3675" t="s">
         <v>72</v>
@@ -90137,7 +90184,7 @@
     </row>
     <row r="3676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3676" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3676" t="s">
         <v>72</v>
@@ -90163,7 +90210,7 @@
     </row>
     <row r="3677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3677" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3677" t="s">
         <v>72</v>
@@ -90189,7 +90236,7 @@
     </row>
     <row r="3678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3678" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3678" t="s">
         <v>72</v>
@@ -90215,7 +90262,7 @@
     </row>
     <row r="3679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3679" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3679" t="s">
         <v>72</v>
@@ -90241,7 +90288,7 @@
     </row>
     <row r="3680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3680" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3680" t="s">
         <v>72</v>
@@ -90267,7 +90314,7 @@
     </row>
     <row r="3681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3681" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3681" t="s">
         <v>73</v>
@@ -90293,7 +90340,7 @@
     </row>
     <row r="3682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3682" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3682" t="s">
         <v>73</v>
@@ -90319,7 +90366,7 @@
     </row>
     <row r="3683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3683" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3683" t="s">
         <v>227</v>
@@ -90345,7 +90392,7 @@
     </row>
     <row r="3684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3684" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3684" t="s">
         <v>227</v>
@@ -90371,7 +90418,7 @@
     </row>
     <row r="3685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3685" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3685" t="s">
         <v>227</v>
@@ -90397,7 +90444,7 @@
     </row>
     <row r="3686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3686" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3686" t="s">
         <v>227</v>
@@ -90423,7 +90470,7 @@
     </row>
     <row r="3687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3687" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3687" t="s">
         <v>227</v>
@@ -90449,7 +90496,7 @@
     </row>
     <row r="3688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3688" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3688" t="s">
         <v>227</v>
@@ -90475,7 +90522,7 @@
     </row>
     <row r="3689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3689" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3689" t="s">
         <v>227</v>
@@ -90501,7 +90548,7 @@
     </row>
     <row r="3690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3690" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3690" t="s">
         <v>229</v>
@@ -90527,7 +90574,7 @@
     </row>
     <row r="3691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3691" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3691" t="s">
         <v>229</v>
@@ -90553,7 +90600,7 @@
     </row>
     <row r="3692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3692" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3692" t="s">
         <v>229</v>
@@ -90579,7 +90626,7 @@
     </row>
     <row r="3693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3693" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3693" t="s">
         <v>229</v>
@@ -90605,7 +90652,7 @@
     </row>
     <row r="3694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3694" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3694" t="s">
         <v>229</v>
@@ -90631,7 +90678,7 @@
     </row>
     <row r="3695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3695" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3695" t="s">
         <v>229</v>
@@ -90657,7 +90704,7 @@
     </row>
     <row r="3696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3696" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B3696" t="s">
         <v>229</v>
@@ -90683,7 +90730,7 @@
     </row>
     <row r="3697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3697" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3697" t="s">
         <v>261</v>
@@ -90698,7 +90745,7 @@
         <v>9.73</v>
       </c>
       <c r="F3697" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3697">
         <v>394565</v>
@@ -90709,7 +90756,7 @@
     </row>
     <row r="3698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3698" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B3698" t="s">
         <v>261</v>
@@ -90724,7 +90771,7 @@
         <v>9.51</v>
       </c>
       <c r="F3698" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3698">
         <v>394582</v>
@@ -90735,7 +90782,7 @@
     </row>
     <row r="3699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3699" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3699" t="s">
         <v>230</v>
@@ -90761,7 +90808,7 @@
     </row>
     <row r="3700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3700" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3700" t="s">
         <v>230</v>
@@ -90787,7 +90834,7 @@
     </row>
     <row r="3701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3701" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3701" t="s">
         <v>230</v>
@@ -90813,7 +90860,7 @@
     </row>
     <row r="3702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3702" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3702" t="s">
         <v>230</v>
@@ -90839,7 +90886,7 @@
     </row>
     <row r="3703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3703" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3703" t="s">
         <v>230</v>
@@ -90865,7 +90912,7 @@
     </row>
     <row r="3704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3704" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3704" t="s">
         <v>230</v>
@@ -90891,7 +90938,7 @@
     </row>
     <row r="3705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3705" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3705" t="s">
         <v>231</v>
@@ -90917,7 +90964,7 @@
     </row>
     <row r="3706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3706" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3706" t="s">
         <v>231</v>
@@ -90943,7 +90990,7 @@
     </row>
     <row r="3707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3707" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3707" t="s">
         <v>231</v>
@@ -90969,7 +91016,7 @@
     </row>
     <row r="3708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3708" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3708" t="s">
         <v>231</v>
@@ -90995,7 +91042,7 @@
     </row>
     <row r="3709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3709" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3709" t="s">
         <v>231</v>
@@ -91021,7 +91068,7 @@
     </row>
     <row r="3710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3710" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3710" t="s">
         <v>231</v>
@@ -91047,7 +91094,7 @@
     </row>
     <row r="3711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3711" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3711" t="s">
         <v>232</v>
@@ -91073,7 +91120,7 @@
     </row>
     <row r="3712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3712" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3712" t="s">
         <v>232</v>
@@ -91099,7 +91146,7 @@
     </row>
     <row r="3713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3713" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3713" t="s">
         <v>232</v>
@@ -91125,7 +91172,7 @@
     </row>
     <row r="3714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3714" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3714" t="s">
         <v>232</v>
@@ -91151,7 +91198,7 @@
     </row>
     <row r="3715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3715" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3715" t="s">
         <v>232</v>
@@ -91177,7 +91224,7 @@
     </row>
     <row r="3716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3716" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3716" t="s">
         <v>232</v>
@@ -91203,7 +91250,7 @@
     </row>
     <row r="3717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3717" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3717" t="s">
         <v>233</v>
@@ -91229,7 +91276,7 @@
     </row>
     <row r="3718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3718" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3718" t="s">
         <v>233</v>
@@ -91255,7 +91302,7 @@
     </row>
     <row r="3719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3719" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3719" t="s">
         <v>233</v>
@@ -91281,7 +91328,7 @@
     </row>
     <row r="3720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3720" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3720" t="s">
         <v>234</v>
@@ -91307,7 +91354,7 @@
     </row>
     <row r="3721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3721" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3721" t="s">
         <v>233</v>
@@ -91333,7 +91380,7 @@
     </row>
     <row r="3722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3722" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3722" t="s">
         <v>233</v>
@@ -91359,7 +91406,7 @@
     </row>
     <row r="3723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3723" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3723" t="s">
         <v>234</v>
@@ -91385,7 +91432,7 @@
     </row>
     <row r="3724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3724" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3724" t="s">
         <v>234</v>
@@ -91411,7 +91458,7 @@
     </row>
     <row r="3725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3725" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3725" t="s">
         <v>234</v>
@@ -91437,7 +91484,7 @@
     </row>
     <row r="3726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3726" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3726" t="s">
         <v>234</v>
@@ -91463,7 +91510,7 @@
     </row>
     <row r="3727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3727" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3727" t="s">
         <v>234</v>
@@ -91489,7 +91536,7 @@
     </row>
     <row r="3728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3728" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3728" t="s">
         <v>233</v>
@@ -91515,7 +91562,7 @@
     </row>
     <row r="3729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3729" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="B3729" t="s">
         <v>261</v>
@@ -91530,7 +91577,7 @@
         <v>11.31</v>
       </c>
       <c r="F3729" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3729">
         <v>394603</v>
@@ -91541,7 +91588,7 @@
     </row>
     <row r="3730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3730" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B3730" t="s">
         <v>261</v>
@@ -91556,7 +91603,7 @@
         <v>11.55</v>
       </c>
       <c r="F3730" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3730">
         <v>394629</v>
@@ -91567,7 +91614,7 @@
     </row>
     <row r="3731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3731" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3731" t="s">
         <v>72</v>
@@ -91593,7 +91640,7 @@
     </row>
     <row r="3732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3732" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3732" t="s">
         <v>69</v>
@@ -91619,7 +91666,7 @@
     </row>
     <row r="3733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3733" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3733" t="s">
         <v>67</v>
@@ -91645,7 +91692,7 @@
     </row>
     <row r="3734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3734" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3734" t="s">
         <v>230</v>
@@ -91671,7 +91718,7 @@
     </row>
     <row r="3735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3735" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3735" t="s">
         <v>229</v>
@@ -91697,7 +91744,7 @@
     </row>
     <row r="3736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3736" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B3736" t="s">
         <v>261</v>
@@ -91712,7 +91759,7 @@
         <v>10.29</v>
       </c>
       <c r="F3736" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3736">
         <v>394708</v>
@@ -91723,7 +91770,7 @@
     </row>
     <row r="3737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3737" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="B3737" t="s">
         <v>261</v>
@@ -91738,7 +91785,7 @@
         <v>11.22</v>
       </c>
       <c r="F3737" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3737">
         <v>394741</v>
@@ -91749,7 +91796,7 @@
     </row>
     <row r="3738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3738" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B3738" t="s">
         <v>261</v>
@@ -91764,7 +91811,7 @@
         <v>11.14</v>
       </c>
       <c r="F3738" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3738">
         <v>394666</v>
@@ -91775,7 +91822,7 @@
     </row>
     <row r="3739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3739" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B3739" t="s">
         <v>261</v>
@@ -91801,7 +91848,7 @@
     </row>
     <row r="3740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3740" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B3740" t="s">
         <v>261</v>
@@ -91816,7 +91863,7 @@
         <v>11.07</v>
       </c>
       <c r="F3740" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3740">
         <v>394699</v>
@@ -91827,7 +91874,7 @@
     </row>
     <row r="3741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3741" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B3741" t="s">
         <v>261</v>
@@ -91842,7 +91889,7 @@
         <v>8.84</v>
       </c>
       <c r="F3741" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="G3741">
         <v>100001</v>
@@ -91853,7 +91900,7 @@
     </row>
     <row r="3742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3742" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3742" t="s">
         <v>40</v>
@@ -91879,7 +91926,7 @@
     </row>
     <row r="3743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3743" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3743" t="s">
         <v>40</v>
@@ -91905,7 +91952,7 @@
     </row>
     <row r="3744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3744" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3744" t="s">
         <v>40</v>
@@ -91931,7 +91978,7 @@
     </row>
     <row r="3745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3745" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3745" t="s">
         <v>40</v>
@@ -91957,7 +92004,7 @@
     </row>
     <row r="3746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3746" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3746" t="s">
         <v>40</v>
@@ -91983,7 +92030,7 @@
     </row>
     <row r="3747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3747" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3747" t="s">
         <v>40</v>
@@ -91998,7 +92045,7 @@
         <v>39.72</v>
       </c>
       <c r="F3747" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3747">
         <v>398577</v>
@@ -92009,7 +92056,7 @@
     </row>
     <row r="3748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3748" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3748" t="s">
         <v>40</v>
@@ -92035,7 +92082,7 @@
     </row>
     <row r="3749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3749" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3749" t="s">
         <v>37</v>
@@ -92061,7 +92108,7 @@
     </row>
     <row r="3750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3750" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3750" t="s">
         <v>35</v>
@@ -92087,7 +92134,7 @@
     </row>
     <row r="3751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3751" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3751" t="s">
         <v>35</v>
@@ -92113,7 +92160,7 @@
     </row>
     <row r="3752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3752" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3752" t="s">
         <v>35</v>
@@ -92128,7 +92175,7 @@
         <v>45.72</v>
       </c>
       <c r="F3752" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3752">
         <v>398583</v>
@@ -92139,7 +92186,7 @@
     </row>
     <row r="3753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3753" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3753" t="s">
         <v>35</v>
@@ -92165,7 +92212,7 @@
     </row>
     <row r="3754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3754" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3754" t="s">
         <v>35</v>
@@ -92191,7 +92238,7 @@
     </row>
     <row r="3755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3755" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3755" t="s">
         <v>35</v>
@@ -92217,7 +92264,7 @@
     </row>
     <row r="3756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3756" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3756" t="s">
         <v>35</v>
@@ -92243,7 +92290,7 @@
     </row>
     <row r="3757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3757" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3757" t="s">
         <v>261</v>
@@ -92258,7 +92305,7 @@
         <v>10</v>
       </c>
       <c r="F3757" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3757">
         <v>394783</v>
@@ -92269,7 +92316,7 @@
     </row>
     <row r="3758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3758" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3758" t="s">
         <v>261</v>
@@ -92295,7 +92342,7 @@
     </row>
     <row r="3759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3759" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B3759" t="s">
         <v>261</v>
@@ -92321,7 +92368,7 @@
     </row>
     <row r="3760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3760" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3760" t="s">
         <v>38</v>
@@ -92347,7 +92394,7 @@
     </row>
     <row r="3761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3761" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3761" t="s">
         <v>39</v>
@@ -92373,7 +92420,7 @@
     </row>
     <row r="3762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3762" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3762" t="s">
         <v>39</v>
@@ -92399,7 +92446,7 @@
     </row>
     <row r="3763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3763" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3763" t="s">
         <v>39</v>
@@ -92425,7 +92472,7 @@
     </row>
     <row r="3764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3764" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3764" t="s">
         <v>39</v>
@@ -92451,7 +92498,7 @@
     </row>
     <row r="3765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3765" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3765" t="s">
         <v>37</v>
@@ -92477,7 +92524,7 @@
     </row>
     <row r="3766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3766" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3766" t="s">
         <v>37</v>
@@ -92503,7 +92550,7 @@
     </row>
     <row r="3767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3767" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3767" t="s">
         <v>37</v>
@@ -92529,7 +92576,7 @@
     </row>
     <row r="3768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3768" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3768" t="s">
         <v>37</v>
@@ -92555,7 +92602,7 @@
     </row>
     <row r="3769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3769" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3769" t="s">
         <v>37</v>
@@ -92581,7 +92628,7 @@
     </row>
     <row r="3770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3770" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3770" t="s">
         <v>37</v>
@@ -92607,7 +92654,7 @@
     </row>
     <row r="3771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3771" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3771" t="s">
         <v>38</v>
@@ -92633,7 +92680,7 @@
     </row>
     <row r="3772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3772" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3772" t="s">
         <v>38</v>
@@ -92659,7 +92706,7 @@
     </row>
     <row r="3773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3773" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3773" t="s">
         <v>38</v>
@@ -92685,7 +92732,7 @@
     </row>
     <row r="3774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3774" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3774" t="s">
         <v>38</v>
@@ -92711,7 +92758,7 @@
     </row>
     <row r="3775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3775" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3775" t="s">
         <v>38</v>
@@ -92737,7 +92784,7 @@
     </row>
     <row r="3776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3776" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3776" t="s">
         <v>261</v>
@@ -92763,7 +92810,7 @@
     </row>
     <row r="3777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3777" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="B3777" t="s">
         <v>261</v>
@@ -92778,7 +92825,7 @@
         <v>10.09</v>
       </c>
       <c r="F3777" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3777">
         <v>394826</v>
@@ -92789,7 +92836,7 @@
     </row>
     <row r="3778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3778" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3778" t="s">
         <v>46</v>
@@ -92815,7 +92862,7 @@
     </row>
     <row r="3779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3779" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3779" t="s">
         <v>46</v>
@@ -92841,7 +92888,7 @@
     </row>
     <row r="3780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3780" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3780" t="s">
         <v>46</v>
@@ -92867,7 +92914,7 @@
     </row>
     <row r="3781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3781" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3781" t="s">
         <v>46</v>
@@ -92893,7 +92940,7 @@
     </row>
     <row r="3782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3782" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3782" t="s">
         <v>46</v>
@@ -92919,7 +92966,7 @@
     </row>
     <row r="3783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3783" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3783" t="s">
         <v>46</v>
@@ -92945,7 +92992,7 @@
     </row>
     <row r="3784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3784" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3784" t="s">
         <v>46</v>
@@ -92960,7 +93007,7 @@
         <v>47.8</v>
       </c>
       <c r="F3784" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3784">
         <v>311762</v>
@@ -92971,7 +93018,7 @@
     </row>
     <row r="3785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3785" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3785" t="s">
         <v>45</v>
@@ -92997,7 +93044,7 @@
     </row>
     <row r="3786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3786" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3786" t="s">
         <v>45</v>
@@ -93023,7 +93070,7 @@
     </row>
     <row r="3787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3787" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3787" t="s">
         <v>45</v>
@@ -93049,7 +93096,7 @@
     </row>
     <row r="3788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3788" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3788" t="s">
         <v>45</v>
@@ -93075,7 +93122,7 @@
     </row>
     <row r="3789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3789" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3789" t="s">
         <v>45</v>
@@ -93090,7 +93137,7 @@
         <v>49.04</v>
       </c>
       <c r="F3789" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3789">
         <v>311771</v>
@@ -93101,7 +93148,7 @@
     </row>
     <row r="3790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3790" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3790" t="s">
         <v>45</v>
@@ -93127,7 +93174,7 @@
     </row>
     <row r="3791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3791" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3791" t="s">
         <v>44</v>
@@ -93153,7 +93200,7 @@
     </row>
     <row r="3792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3792" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3792" t="s">
         <v>44</v>
@@ -93179,7 +93226,7 @@
     </row>
     <row r="3793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3793" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3793" t="s">
         <v>44</v>
@@ -93205,7 +93252,7 @@
     </row>
     <row r="3794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3794" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3794" t="s">
         <v>44</v>
@@ -93231,7 +93278,7 @@
     </row>
     <row r="3795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3795" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3795" t="s">
         <v>44</v>
@@ -93257,7 +93304,7 @@
     </row>
     <row r="3796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3796" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3796" t="s">
         <v>44</v>
@@ -93272,7 +93319,7 @@
         <v>34.520000000000003</v>
       </c>
       <c r="F3796" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3796">
         <v>311774</v>
@@ -93283,7 +93330,7 @@
     </row>
     <row r="3797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3797" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3797" t="s">
         <v>44</v>
@@ -93309,7 +93356,7 @@
     </row>
     <row r="3798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3798" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3798" t="s">
         <v>43</v>
@@ -93335,7 +93382,7 @@
     </row>
     <row r="3799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3799" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3799" t="s">
         <v>43</v>
@@ -93361,7 +93408,7 @@
     </row>
     <row r="3800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3800" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3800" t="s">
         <v>43</v>
@@ -93387,7 +93434,7 @@
     </row>
     <row r="3801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3801" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3801" t="s">
         <v>43</v>
@@ -93413,7 +93460,7 @@
     </row>
     <row r="3802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3802" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3802" t="s">
         <v>43</v>
@@ -93428,7 +93475,7 @@
         <v>45.46</v>
       </c>
       <c r="F3802" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3802">
         <v>311782</v>
@@ -93439,7 +93486,7 @@
     </row>
     <row r="3803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3803" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3803" t="s">
         <v>43</v>
@@ -93465,7 +93512,7 @@
     </row>
     <row r="3804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3804" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3804" t="s">
         <v>42</v>
@@ -93491,7 +93538,7 @@
     </row>
     <row r="3805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3805" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3805" t="s">
         <v>42</v>
@@ -93517,7 +93564,7 @@
     </row>
     <row r="3806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3806" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3806" t="s">
         <v>42</v>
@@ -93543,7 +93590,7 @@
     </row>
     <row r="3807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3807" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3807" t="s">
         <v>42</v>
@@ -93569,7 +93616,7 @@
     </row>
     <row r="3808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3808" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3808" t="s">
         <v>42</v>
@@ -93595,7 +93642,7 @@
     </row>
     <row r="3809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3809" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3809" t="s">
         <v>42</v>
@@ -93610,7 +93657,7 @@
         <v>45.78</v>
       </c>
       <c r="F3809" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3809">
         <v>311786</v>
@@ -93621,7 +93668,7 @@
     </row>
     <row r="3810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3810" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3810" t="s">
         <v>41</v>
@@ -93647,7 +93694,7 @@
     </row>
     <row r="3811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3811" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3811" t="s">
         <v>41</v>
@@ -93673,7 +93720,7 @@
     </row>
     <row r="3812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3812" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B3812" t="s">
         <v>261</v>
@@ -93688,7 +93735,7 @@
         <v>10.61</v>
       </c>
       <c r="F3812" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3812">
         <v>333764</v>
@@ -93699,7 +93746,7 @@
     </row>
     <row r="3813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3813" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3813" t="s">
         <v>41</v>
@@ -93725,7 +93772,7 @@
     </row>
     <row r="3814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3814" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3814" t="s">
         <v>41</v>
@@ -93751,7 +93798,7 @@
     </row>
     <row r="3815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3815" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3815" t="s">
         <v>47</v>
@@ -93777,7 +93824,7 @@
     </row>
     <row r="3816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3816" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3816" t="s">
         <v>47</v>
@@ -93792,7 +93839,7 @@
         <v>47.54</v>
       </c>
       <c r="F3816" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3816">
         <v>311609</v>
@@ -93803,7 +93850,7 @@
     </row>
     <row r="3817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3817" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3817" t="s">
         <v>47</v>
@@ -93829,7 +93876,7 @@
     </row>
     <row r="3818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3818" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3818" t="s">
         <v>47</v>
@@ -93855,7 +93902,7 @@
     </row>
     <row r="3819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3819" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3819" t="s">
         <v>47</v>
@@ -93881,7 +93928,7 @@
     </row>
     <row r="3820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3820" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3820" t="s">
         <v>47</v>
@@ -93907,7 +93954,7 @@
     </row>
     <row r="3821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3821" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3821" t="s">
         <v>47</v>
@@ -93933,7 +93980,7 @@
     </row>
     <row r="3822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3822" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3822" t="s">
         <v>47</v>
@@ -93959,7 +94006,7 @@
     </row>
     <row r="3823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3823" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3823" t="s">
         <v>48</v>
@@ -93985,7 +94032,7 @@
     </row>
     <row r="3824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3824" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3824" t="s">
         <v>48</v>
@@ -94011,7 +94058,7 @@
     </row>
     <row r="3825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3825" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3825" t="s">
         <v>48</v>
@@ -94037,7 +94084,7 @@
     </row>
     <row r="3826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3826" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3826" t="s">
         <v>48</v>
@@ -94063,7 +94110,7 @@
     </row>
     <row r="3827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3827" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3827" t="s">
         <v>48</v>
@@ -94089,7 +94136,7 @@
     </row>
     <row r="3828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3828" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3828" t="s">
         <v>48</v>
@@ -94104,7 +94151,7 @@
         <v>48.7</v>
       </c>
       <c r="F3828" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G3828">
         <v>311606</v>
@@ -94115,7 +94162,7 @@
     </row>
     <row r="3829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3829" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3829" t="s">
         <v>48</v>
@@ -94141,7 +94188,7 @@
     </row>
     <row r="3830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3830" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3830" t="s">
         <v>49</v>
@@ -94167,7 +94214,7 @@
     </row>
     <row r="3831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3831" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3831" t="s">
         <v>49</v>
@@ -94193,7 +94240,7 @@
     </row>
     <row r="3832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3832" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3832" t="s">
         <v>49</v>
@@ -94219,7 +94266,7 @@
     </row>
     <row r="3833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3833" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3833" t="s">
         <v>49</v>
@@ -94234,7 +94281,7 @@
         <v>53.42</v>
       </c>
       <c r="F3833" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3833">
         <v>311796</v>
@@ -94245,7 +94292,7 @@
     </row>
     <row r="3834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3834" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3834" t="s">
         <v>49</v>
@@ -94271,7 +94318,7 @@
     </row>
     <row r="3835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3835" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3835" t="s">
         <v>49</v>
@@ -94297,7 +94344,7 @@
     </row>
     <row r="3836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3836" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3836" t="s">
         <v>49</v>
@@ -94323,7 +94370,7 @@
     </row>
     <row r="3837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3837" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3837" t="s">
         <v>49</v>
@@ -94349,7 +94396,7 @@
     </row>
     <row r="3838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3838" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3838" t="s">
         <v>50</v>
@@ -94375,7 +94422,7 @@
     </row>
     <row r="3839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3839" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3839" t="s">
         <v>261</v>
@@ -94401,7 +94448,7 @@
     </row>
     <row r="3840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3840" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3840" t="s">
         <v>261</v>
@@ -94416,7 +94463,7 @@
         <v>9.9</v>
       </c>
       <c r="F3840" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3840">
         <v>333805</v>
@@ -94427,7 +94474,7 @@
     </row>
     <row r="3841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3841" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B3841" t="s">
         <v>261</v>
@@ -94442,7 +94489,7 @@
         <v>9.5299999999999994</v>
       </c>
       <c r="F3841" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3841">
         <v>333856</v>
@@ -94453,7 +94500,7 @@
     </row>
     <row r="3842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3842" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B3842" t="s">
         <v>261</v>
@@ -94479,7 +94526,7 @@
     </row>
     <row r="3843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3843" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B3843" t="s">
         <v>261</v>
@@ -94505,7 +94552,7 @@
     </row>
     <row r="3844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3844" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B3844" t="s">
         <v>261</v>
@@ -94520,7 +94567,7 @@
         <v>10.3</v>
       </c>
       <c r="F3844" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3844">
         <v>333907</v>
@@ -94531,7 +94578,7 @@
     </row>
     <row r="3845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3845" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B3845" t="s">
         <v>261</v>
@@ -94557,7 +94604,7 @@
     </row>
     <row r="3846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3846" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B3846" t="s">
         <v>261</v>
@@ -94572,7 +94619,7 @@
         <v>10.45</v>
       </c>
       <c r="F3846" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3846">
         <v>333948</v>
@@ -94583,7 +94630,7 @@
     </row>
     <row r="3847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3847" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B3847" t="s">
         <v>261</v>
@@ -94598,7 +94645,7 @@
         <v>11.39</v>
       </c>
       <c r="F3847" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3847">
         <v>333957</v>
@@ -94609,7 +94656,7 @@
     </row>
     <row r="3848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3848" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B3848" t="s">
         <v>261</v>
@@ -94624,7 +94671,7 @@
         <v>8.57</v>
       </c>
       <c r="F3848" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3848">
         <v>333979</v>
@@ -94635,7 +94682,7 @@
     </row>
     <row r="3849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3849" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B3849" t="s">
         <v>258</v>
@@ -94661,7 +94708,7 @@
     </row>
     <row r="3850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3850" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B3850" t="s">
         <v>258</v>
@@ -94676,7 +94723,7 @@
         <v>12</v>
       </c>
       <c r="F3850" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3850">
         <v>334014</v>
@@ -94687,7 +94734,7 @@
     </row>
     <row r="3851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3851" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B3851" t="s">
         <v>258</v>
@@ -94702,7 +94749,7 @@
         <v>9.69</v>
       </c>
       <c r="F3851" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3851">
         <v>334018</v>
@@ -94713,7 +94760,7 @@
     </row>
     <row r="3852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3852" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3852" t="s">
         <v>35</v>
@@ -94739,7 +94786,7 @@
     </row>
     <row r="3853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3853" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3853" t="s">
         <v>35</v>
@@ -94765,7 +94812,7 @@
     </row>
     <row r="3854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3854" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3854" t="s">
         <v>38</v>
@@ -94791,7 +94838,7 @@
     </row>
     <row r="3855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3855" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3855" t="s">
         <v>39</v>
@@ -94817,7 +94864,7 @@
     </row>
     <row r="3856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3856" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3856" t="s">
         <v>103</v>
@@ -94843,7 +94890,7 @@
     </row>
     <row r="3857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3857" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3857" t="s">
         <v>103</v>
@@ -94869,7 +94916,7 @@
     </row>
     <row r="3858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3858" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3858" t="s">
         <v>261</v>
@@ -94895,7 +94942,7 @@
     </row>
     <row r="3859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3859" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3859" t="s">
         <v>258</v>
@@ -94910,7 +94957,7 @@
         <v>10.130000000000001</v>
       </c>
       <c r="F3859" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3859">
         <v>334064</v>
@@ -94921,7 +94968,7 @@
     </row>
     <row r="3860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3860" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B3860" t="s">
         <v>258</v>
@@ -94936,7 +94983,7 @@
         <v>11.6</v>
       </c>
       <c r="F3860" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3860">
         <v>334067</v>
@@ -94947,7 +94994,7 @@
     </row>
     <row r="3861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3861" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3861" t="s">
         <v>49</v>
@@ -94973,7 +95020,7 @@
     </row>
     <row r="3862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3862" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3862" t="s">
         <v>48</v>
@@ -94999,7 +95046,7 @@
     </row>
     <row r="3863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3863" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3863" t="s">
         <v>47</v>
@@ -95025,7 +95072,7 @@
     </row>
     <row r="3864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3864" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3864" t="s">
         <v>45</v>
@@ -95051,7 +95098,7 @@
     </row>
     <row r="3865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3865" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3865" t="s">
         <v>45</v>
@@ -95077,7 +95124,7 @@
     </row>
     <row r="3866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3866" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3866" t="s">
         <v>44</v>
@@ -95103,7 +95150,7 @@
     </row>
     <row r="3867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3867" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3867" t="s">
         <v>43</v>
@@ -95129,7 +95176,7 @@
     </row>
     <row r="3868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3868" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3868" t="s">
         <v>43</v>
@@ -95155,7 +95202,7 @@
     </row>
     <row r="3869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3869" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3869" t="s">
         <v>42</v>
@@ -95181,7 +95228,7 @@
     </row>
     <row r="3870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3870" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3870" t="s">
         <v>41</v>
@@ -95207,7 +95254,7 @@
     </row>
     <row r="3871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3871" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3871" t="s">
         <v>41</v>
@@ -95233,7 +95280,7 @@
     </row>
     <row r="3872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3872" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3872" t="s">
         <v>103</v>
@@ -95259,7 +95306,7 @@
     </row>
     <row r="3873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3873" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3873" t="s">
         <v>103</v>
@@ -95274,7 +95321,7 @@
         <v>46.6</v>
       </c>
       <c r="F3873" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3873">
         <v>311623</v>
@@ -95285,7 +95332,7 @@
     </row>
     <row r="3874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3874" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3874" t="s">
         <v>103</v>
@@ -95311,7 +95358,7 @@
     </row>
     <row r="3875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3875" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3875" t="s">
         <v>103</v>
@@ -95337,7 +95384,7 @@
     </row>
     <row r="3876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3876" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3876" t="s">
         <v>103</v>
@@ -95363,7 +95410,7 @@
     </row>
     <row r="3877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3877" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3877" t="s">
         <v>103</v>
@@ -95389,7 +95436,7 @@
     </row>
     <row r="3878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3878" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3878" t="s">
         <v>103</v>
@@ -95415,7 +95462,7 @@
     </row>
     <row r="3879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3879" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3879" t="s">
         <v>258</v>
@@ -95441,7 +95488,7 @@
     </row>
     <row r="3880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3880" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3880" t="s">
         <v>258</v>
@@ -95456,7 +95503,7 @@
         <v>10.37</v>
       </c>
       <c r="F3880" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3880">
         <v>334105</v>
@@ -95467,7 +95514,7 @@
     </row>
     <row r="3881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3881" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3881" t="s">
         <v>258</v>
@@ -95482,7 +95529,7 @@
         <v>10.02</v>
       </c>
       <c r="F3881" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3881">
         <v>334126</v>
@@ -95493,7 +95540,7 @@
     </row>
     <row r="3882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3882" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3882" t="s">
         <v>258</v>
@@ -95519,7 +95566,7 @@
     </row>
     <row r="3883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3883" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B3883" t="s">
         <v>258</v>
@@ -95534,7 +95581,7 @@
         <v>7.66</v>
       </c>
       <c r="F3883" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3883">
         <v>334136</v>
@@ -95545,7 +95592,7 @@
     </row>
     <row r="3884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3884" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3884" t="s">
         <v>123</v>
@@ -95571,7 +95618,7 @@
     </row>
     <row r="3885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3885" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3885" t="s">
         <v>123</v>
@@ -95597,7 +95644,7 @@
     </row>
     <row r="3886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3886" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3886" t="s">
         <v>123</v>
@@ -95623,7 +95670,7 @@
     </row>
     <row r="3887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3887" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3887" t="s">
         <v>123</v>
@@ -95638,7 +95685,7 @@
         <v>51.72</v>
       </c>
       <c r="F3887" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3887">
         <v>311650</v>
@@ -95649,7 +95696,7 @@
     </row>
     <row r="3888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3888" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3888" t="s">
         <v>123</v>
@@ -95675,7 +95722,7 @@
     </row>
     <row r="3889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3889" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3889" t="s">
         <v>123</v>
@@ -95701,7 +95748,7 @@
     </row>
     <row r="3890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3890" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3890" t="s">
         <v>122</v>
@@ -95727,7 +95774,7 @@
     </row>
     <row r="3891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3891" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3891" t="s">
         <v>122</v>
@@ -95753,7 +95800,7 @@
     </row>
     <row r="3892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3892" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3892" t="s">
         <v>122</v>
@@ -95779,7 +95826,7 @@
     </row>
     <row r="3893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3893" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3893" t="s">
         <v>122</v>
@@ -95805,7 +95852,7 @@
     </row>
     <row r="3894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3894" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3894" t="s">
         <v>122</v>
@@ -95831,7 +95878,7 @@
     </row>
     <row r="3895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3895" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3895" t="s">
         <v>122</v>
@@ -95857,7 +95904,7 @@
     </row>
     <row r="3896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3896" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3896" t="s">
         <v>121</v>
@@ -95883,7 +95930,7 @@
     </row>
     <row r="3897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3897" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3897" t="s">
         <v>121</v>
@@ -95909,7 +95956,7 @@
     </row>
     <row r="3898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3898" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3898" t="s">
         <v>121</v>
@@ -95935,7 +95982,7 @@
     </row>
     <row r="3899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3899" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3899" t="s">
         <v>121</v>
@@ -95950,7 +95997,7 @@
         <v>49.38</v>
       </c>
       <c r="F3899" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3899">
         <v>312162</v>
@@ -95961,7 +96008,7 @@
     </row>
     <row r="3900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3900" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3900" t="s">
         <v>121</v>
@@ -95987,7 +96034,7 @@
     </row>
     <row r="3901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3901" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3901" t="s">
         <v>120</v>
@@ -96013,7 +96060,7 @@
     </row>
     <row r="3902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3902" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3902" t="s">
         <v>120</v>
@@ -96039,7 +96086,7 @@
     </row>
     <row r="3903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3903" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3903" t="s">
         <v>120</v>
@@ -96065,7 +96112,7 @@
     </row>
     <row r="3904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3904" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3904" t="s">
         <v>120</v>
@@ -96091,7 +96138,7 @@
     </row>
     <row r="3905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3905" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3905" t="s">
         <v>120</v>
@@ -96117,7 +96164,7 @@
     </row>
     <row r="3906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3906" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3906" t="s">
         <v>120</v>
@@ -96143,7 +96190,7 @@
     </row>
     <row r="3907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3907" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3907" t="s">
         <v>124</v>
@@ -96169,7 +96216,7 @@
     </row>
     <row r="3908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3908" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3908" t="s">
         <v>103</v>
@@ -96195,7 +96242,7 @@
     </row>
     <row r="3909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3909" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3909" t="s">
         <v>103</v>
@@ -96221,7 +96268,7 @@
     </row>
     <row r="3910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3910" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3910" t="s">
         <v>46</v>
@@ -96247,7 +96294,7 @@
     </row>
     <row r="3911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3911" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3911" t="s">
         <v>45</v>
@@ -96273,7 +96320,7 @@
     </row>
     <row r="3912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3912" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3912" t="s">
         <v>258</v>
@@ -96288,7 +96335,7 @@
         <v>11.25</v>
       </c>
       <c r="F3912" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3912">
         <v>334179</v>
@@ -96299,7 +96346,7 @@
     </row>
     <row r="3913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3913" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3913" t="s">
         <v>258</v>
@@ -96325,7 +96372,7 @@
     </row>
     <row r="3914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3914" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B3914" t="s">
         <v>258</v>
@@ -96340,7 +96387,7 @@
         <v>9.41</v>
       </c>
       <c r="F3914" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3914">
         <v>334163</v>
@@ -96351,7 +96398,7 @@
     </row>
     <row r="3915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3915" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B3915" t="s">
         <v>121</v>
@@ -96377,7 +96424,7 @@
     </row>
     <row r="3916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3916" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B3916" t="s">
         <v>258</v>
@@ -96403,7 +96450,7 @@
     </row>
     <row r="3917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3917" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B3917" t="s">
         <v>258</v>
@@ -96418,7 +96465,7 @@
         <v>10.09</v>
       </c>
       <c r="F3917" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3917">
         <v>334236</v>
@@ -96429,7 +96476,7 @@
     </row>
     <row r="3918" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3918" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B3918" t="s">
         <v>258</v>
@@ -96444,7 +96491,7 @@
         <v>11.08</v>
       </c>
       <c r="F3918" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3918">
         <v>334233</v>
@@ -96455,7 +96502,7 @@
     </row>
     <row r="3919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3919" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B3919" t="s">
         <v>258</v>
@@ -96481,7 +96528,7 @@
     </row>
     <row r="3920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3920" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B3920" t="s">
         <v>258</v>
@@ -96496,7 +96543,7 @@
         <v>11.7</v>
       </c>
       <c r="F3920" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3920">
         <v>334272</v>
@@ -96507,7 +96554,7 @@
     </row>
     <row r="3921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3921" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B3921" t="s">
         <v>258</v>
@@ -96522,7 +96569,7 @@
         <v>8.18</v>
       </c>
       <c r="F3921" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3921">
         <v>334269</v>
@@ -96533,7 +96580,7 @@
     </row>
     <row r="3922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3922" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B3922" t="s">
         <v>258</v>
@@ -96559,7 +96606,7 @@
     </row>
     <row r="3923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3923" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B3923" t="s">
         <v>258</v>
@@ -96574,7 +96621,7 @@
         <v>9.85</v>
       </c>
       <c r="F3923" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3923">
         <v>334315</v>
@@ -96585,7 +96632,7 @@
     </row>
     <row r="3924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3924" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B3924" t="s">
         <v>258</v>
@@ -96600,7 +96647,7 @@
         <v>8.66</v>
       </c>
       <c r="F3924" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3924">
         <v>334310</v>
@@ -96611,7 +96658,7 @@
     </row>
     <row r="3925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3925" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3925" t="s">
         <v>122</v>
@@ -96637,7 +96684,7 @@
     </row>
     <row r="3926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3926" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3926" t="s">
         <v>122</v>
@@ -96663,7 +96710,7 @@
     </row>
     <row r="3927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3927" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3927" t="s">
         <v>124</v>
@@ -96689,7 +96736,7 @@
     </row>
     <row r="3928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3928" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3928" t="s">
         <v>258</v>
@@ -96715,7 +96762,7 @@
     </row>
     <row r="3929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3929" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3929" t="s">
         <v>258</v>
@@ -96730,7 +96777,7 @@
         <v>10.78</v>
       </c>
       <c r="F3929" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3929">
         <v>334389</v>
@@ -96741,7 +96788,7 @@
     </row>
     <row r="3930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3930" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B3930" t="s">
         <v>258</v>
@@ -96756,7 +96803,7 @@
         <v>9.9</v>
       </c>
       <c r="F3930" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3930">
         <v>334371</v>
@@ -96767,7 +96814,7 @@
     </row>
     <row r="3931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3931" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B3931" t="s">
         <v>258</v>
@@ -96793,7 +96840,7 @@
     </row>
     <row r="3932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3932" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B3932" t="s">
         <v>258</v>
@@ -96808,7 +96855,7 @@
         <v>10.91</v>
       </c>
       <c r="F3932" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3932">
         <v>334454</v>
@@ -96819,7 +96866,7 @@
     </row>
     <row r="3933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3933" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B3933" t="s">
         <v>258</v>
@@ -96834,7 +96881,7 @@
         <v>8.23</v>
       </c>
       <c r="F3933" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3933">
         <v>334441</v>
@@ -96845,7 +96892,7 @@
     </row>
     <row r="3934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3934" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3934" t="s">
         <v>85</v>
@@ -96871,7 +96918,7 @@
     </row>
     <row r="3935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3935" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3935" t="s">
         <v>85</v>
@@ -96897,7 +96944,7 @@
     </row>
     <row r="3936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3936" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3936" t="s">
         <v>85</v>
@@ -96923,7 +96970,7 @@
     </row>
     <row r="3937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3937" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3937" t="s">
         <v>85</v>
@@ -96949,7 +96996,7 @@
     </row>
     <row r="3938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3938" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3938" t="s">
         <v>85</v>
@@ -96975,7 +97022,7 @@
     </row>
     <row r="3939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3939" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3939" t="s">
         <v>85</v>
@@ -97001,7 +97048,7 @@
     </row>
     <row r="3940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3940" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3940" t="s">
         <v>86</v>
@@ -97016,7 +97063,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="F3940" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3940">
         <v>312191</v>
@@ -97027,7 +97074,7 @@
     </row>
     <row r="3941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3941" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3941" t="s">
         <v>86</v>
@@ -97053,7 +97100,7 @@
     </row>
     <row r="3942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3942" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3942" t="s">
         <v>86</v>
@@ -97079,7 +97126,7 @@
     </row>
     <row r="3943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3943" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3943" t="s">
         <v>86</v>
@@ -97105,7 +97152,7 @@
     </row>
     <row r="3944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3944" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3944" t="s">
         <v>86</v>
@@ -97131,7 +97178,7 @@
     </row>
     <row r="3945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3945" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3945" t="s">
         <v>86</v>
@@ -97157,7 +97204,7 @@
     </row>
     <row r="3946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3946" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3946" t="s">
         <v>87</v>
@@ -97183,7 +97230,7 @@
     </row>
     <row r="3947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3947" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3947" t="s">
         <v>87</v>
@@ -97198,7 +97245,7 @@
         <v>41.72</v>
       </c>
       <c r="F3947" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3947">
         <v>312198</v>
@@ -97209,7 +97256,7 @@
     </row>
     <row r="3948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3948" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3948" t="s">
         <v>87</v>
@@ -97235,7 +97282,7 @@
     </row>
     <row r="3949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3949" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3949" t="s">
         <v>87</v>
@@ -97261,7 +97308,7 @@
     </row>
     <row r="3950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3950" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3950" t="s">
         <v>87</v>
@@ -97287,7 +97334,7 @@
     </row>
     <row r="3951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3951" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3951" t="s">
         <v>87</v>
@@ -97313,7 +97360,7 @@
     </row>
     <row r="3952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3952" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3952" t="s">
         <v>88</v>
@@ -97339,7 +97386,7 @@
     </row>
     <row r="3953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3953" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3953" t="s">
         <v>88</v>
@@ -97365,7 +97412,7 @@
     </row>
     <row r="3954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3954" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3954" t="s">
         <v>88</v>
@@ -97391,7 +97438,7 @@
     </row>
     <row r="3955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3955" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3955" t="s">
         <v>88</v>
@@ -97417,7 +97464,7 @@
     </row>
     <row r="3956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3956" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3956" t="s">
         <v>88</v>
@@ -97443,7 +97490,7 @@
     </row>
     <row r="3957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3957" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3957" t="s">
         <v>89</v>
@@ -97469,7 +97516,7 @@
     </row>
     <row r="3958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3958" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3958" t="s">
         <v>89</v>
@@ -97495,7 +97542,7 @@
     </row>
     <row r="3959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3959" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3959" t="s">
         <v>89</v>
@@ -97521,7 +97568,7 @@
     </row>
     <row r="3960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3960" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3960" t="s">
         <v>89</v>
@@ -97547,7 +97594,7 @@
     </row>
     <row r="3961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3961" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3961" t="s">
         <v>89</v>
@@ -97562,7 +97609,7 @@
         <v>27.86</v>
       </c>
       <c r="F3961" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3961">
         <v>335511</v>
@@ -97573,7 +97620,7 @@
     </row>
     <row r="3962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3962" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3962" t="s">
         <v>89</v>
@@ -97599,7 +97646,7 @@
     </row>
     <row r="3963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3963" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3963" t="s">
         <v>90</v>
@@ -97625,7 +97672,7 @@
     </row>
     <row r="3964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3964" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3964" t="s">
         <v>90</v>
@@ -97651,7 +97698,7 @@
     </row>
     <row r="3965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3965" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3965" t="s">
         <v>90</v>
@@ -97677,7 +97724,7 @@
     </row>
     <row r="3966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3966" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3966" t="s">
         <v>90</v>
@@ -97703,7 +97750,7 @@
     </row>
     <row r="3967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3967" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3967" t="s">
         <v>90</v>
@@ -97729,7 +97776,7 @@
     </row>
     <row r="3968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3968" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3968" t="s">
         <v>91</v>
@@ -97755,7 +97802,7 @@
     </row>
     <row r="3969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3969" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3969" t="s">
         <v>91</v>
@@ -97781,7 +97828,7 @@
     </row>
     <row r="3970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3970" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3970" t="s">
         <v>91</v>
@@ -97807,7 +97854,7 @@
     </row>
     <row r="3971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3971" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3971" t="s">
         <v>91</v>
@@ -97833,7 +97880,7 @@
     </row>
     <row r="3972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3972" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3972" t="s">
         <v>91</v>
@@ -97859,7 +97906,7 @@
     </row>
     <row r="3973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3973" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3973" t="s">
         <v>92</v>
@@ -97885,7 +97932,7 @@
     </row>
     <row r="3974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3974" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3974" t="s">
         <v>92</v>
@@ -97911,7 +97958,7 @@
     </row>
     <row r="3975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3975" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3975" t="s">
         <v>92</v>
@@ -97937,7 +97984,7 @@
     </row>
     <row r="3976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3976" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3976" t="s">
         <v>92</v>
@@ -97952,7 +97999,7 @@
         <v>37.340000000000003</v>
       </c>
       <c r="F3976" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="G3976">
         <v>335524</v>
@@ -97963,7 +98010,7 @@
     </row>
     <row r="3977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3977" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3977" t="s">
         <v>92</v>
@@ -97989,7 +98036,7 @@
     </row>
     <row r="3978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3978" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3978" t="s">
         <v>93</v>
@@ -98015,7 +98062,7 @@
     </row>
     <row r="3979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3979" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3979" t="s">
         <v>422</v>
@@ -98030,7 +98077,7 @@
         <v>8.77</v>
       </c>
       <c r="F3979" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3979">
         <v>334533</v>
@@ -98041,7 +98088,7 @@
     </row>
     <row r="3980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3980" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3980" t="s">
         <v>422</v>
@@ -98056,7 +98103,7 @@
         <v>8.35</v>
       </c>
       <c r="F3980" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3980">
         <v>334520</v>
@@ -98067,7 +98114,7 @@
     </row>
     <row r="3981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3981" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B3981" t="s">
         <v>422</v>
@@ -98093,7 +98140,7 @@
     </row>
     <row r="3982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3982" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B3982" t="s">
         <v>259</v>
@@ -98108,7 +98155,7 @@
         <v>17.47</v>
       </c>
       <c r="F3982" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3982">
         <v>334590</v>
@@ -98119,7 +98166,7 @@
     </row>
     <row r="3983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3983" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B3983" t="s">
         <v>259</v>
@@ -98145,7 +98192,7 @@
     </row>
     <row r="3984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3984" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B3984" t="s">
         <v>422</v>
@@ -98160,7 +98207,7 @@
         <v>8.18</v>
       </c>
       <c r="F3984" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3984">
         <v>334597</v>
@@ -98171,7 +98218,7 @@
     </row>
     <row r="3985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3985" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B3985" t="s">
         <v>88</v>
@@ -98197,7 +98244,7 @@
     </row>
     <row r="3986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3986" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B3986" t="s">
         <v>92</v>
@@ -98223,7 +98270,7 @@
     </row>
     <row r="3987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3987" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B3987" t="s">
         <v>422</v>
@@ -98238,7 +98285,7 @@
         <v>8.24</v>
       </c>
       <c r="F3987" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3987">
         <v>334654</v>
@@ -98249,7 +98296,7 @@
     </row>
     <row r="3988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3988" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B3988" t="s">
         <v>259</v>
@@ -98275,7 +98322,7 @@
     </row>
     <row r="3989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3989" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B3989" t="s">
         <v>259</v>
@@ -98290,7 +98337,7 @@
         <v>14.87</v>
       </c>
       <c r="F3989" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3989">
         <v>334652</v>
@@ -98301,7 +98348,7 @@
     </row>
     <row r="3990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3990" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B3990" t="s">
         <v>93</v>
@@ -98327,7 +98374,7 @@
     </row>
     <row r="3991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3991" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B3991" t="s">
         <v>259</v>
@@ -98353,7 +98400,7 @@
     </row>
     <row r="3992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3992" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B3992" t="s">
         <v>259</v>
@@ -98368,7 +98415,7 @@
         <v>11.33</v>
       </c>
       <c r="F3992" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3992">
         <v>334712</v>
@@ -98379,7 +98426,7 @@
     </row>
     <row r="3993" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3993" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B3993" t="s">
         <v>259</v>
@@ -98394,7 +98441,7 @@
         <v>12.56</v>
       </c>
       <c r="F3993" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3993">
         <v>334735</v>
@@ -98405,7 +98452,7 @@
     </row>
     <row r="3994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3994" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B3994" t="s">
         <v>259</v>
@@ -98431,7 +98478,7 @@
     </row>
     <row r="3995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3995" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B3995" t="s">
         <v>259</v>
@@ -98446,7 +98493,7 @@
         <v>10.92</v>
       </c>
       <c r="F3995" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3995">
         <v>334642</v>
@@ -98457,7 +98504,7 @@
     </row>
     <row r="3996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3996" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B3996" t="s">
         <v>259</v>
@@ -98472,12 +98519,3080 @@
         <v>10.84</v>
       </c>
       <c r="F3996" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3996">
         <v>334636</v>
       </c>
       <c r="H3996" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3997" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3997" t="s">
+        <v>945</v>
+      </c>
+      <c r="B3997" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3997" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3997">
+        <v>6</v>
+      </c>
+      <c r="E3997">
+        <v>43.66</v>
+      </c>
+      <c r="F3997" t="s">
+        <v>902</v>
+      </c>
+      <c r="G3997">
+        <v>335533</v>
+      </c>
+      <c r="H3997" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3998" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3998" t="s">
+        <v>945</v>
+      </c>
+      <c r="B3998" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3998" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3998">
+        <v>6</v>
+      </c>
+      <c r="E3998">
+        <v>45.98</v>
+      </c>
+      <c r="F3998" t="s">
+        <v>733</v>
+      </c>
+      <c r="G3998">
+        <v>335534</v>
+      </c>
+      <c r="H3998" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3999" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3999" t="s">
+        <v>945</v>
+      </c>
+      <c r="B3999" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3999" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3999">
+        <v>6</v>
+      </c>
+      <c r="E3999">
+        <v>40.659999999999997</v>
+      </c>
+      <c r="F3999" t="s">
+        <v>730</v>
+      </c>
+      <c r="G3999">
+        <v>335535</v>
+      </c>
+      <c r="H3999" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4000" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4000" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4000" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4000" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4000">
+        <v>6</v>
+      </c>
+      <c r="E4000">
+        <v>44.14</v>
+      </c>
+      <c r="F4000" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4000">
+        <v>335536</v>
+      </c>
+      <c r="H4000" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4001" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4001" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4001" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4001">
+        <v>6</v>
+      </c>
+      <c r="E4001">
+        <v>47.46</v>
+      </c>
+      <c r="F4001" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4001">
+        <v>335537</v>
+      </c>
+      <c r="H4001" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4002" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4002" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4002" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4002">
+        <v>6</v>
+      </c>
+      <c r="E4002">
+        <v>45.46</v>
+      </c>
+      <c r="F4002" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4002">
+        <v>335538</v>
+      </c>
+      <c r="H4002" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4003" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4003" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4003" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4003">
+        <v>5</v>
+      </c>
+      <c r="E4003">
+        <v>40.4</v>
+      </c>
+      <c r="F4003" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4003">
+        <v>335544</v>
+      </c>
+      <c r="H4003" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4004" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4004" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4004" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4004">
+        <v>6</v>
+      </c>
+      <c r="E4004">
+        <v>48.56</v>
+      </c>
+      <c r="F4004" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4004">
+        <v>335539</v>
+      </c>
+      <c r="H4004" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4005" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4005" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4005" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4005">
+        <v>6</v>
+      </c>
+      <c r="E4005">
+        <v>43.62</v>
+      </c>
+      <c r="F4005" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4005">
+        <v>335540</v>
+      </c>
+      <c r="H4005" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4006" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4006" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4006" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4006">
+        <v>6</v>
+      </c>
+      <c r="E4006">
+        <v>41.22</v>
+      </c>
+      <c r="F4006" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4006">
+        <v>335541</v>
+      </c>
+      <c r="H4006" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4007" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4007" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4007" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4007">
+        <v>6</v>
+      </c>
+      <c r="E4007">
+        <v>44.34</v>
+      </c>
+      <c r="F4007" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4007">
+        <v>335542</v>
+      </c>
+      <c r="H4007" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4008" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4008" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4008" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4008">
+        <v>6</v>
+      </c>
+      <c r="E4008">
+        <v>43.26</v>
+      </c>
+      <c r="F4008" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4008">
+        <v>335543</v>
+      </c>
+      <c r="H4008" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4009" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4009" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4009" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4009">
+        <v>6</v>
+      </c>
+      <c r="E4009">
+        <v>28.9</v>
+      </c>
+      <c r="F4009" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4009">
+        <v>335546</v>
+      </c>
+      <c r="H4009" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4010" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4010" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4010" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4010">
+        <v>6</v>
+      </c>
+      <c r="E4010">
+        <v>40.04</v>
+      </c>
+      <c r="F4010" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4010">
+        <v>335548</v>
+      </c>
+      <c r="H4010" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4011" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4011" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4011" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4011">
+        <v>5</v>
+      </c>
+      <c r="E4011">
+        <v>42.76</v>
+      </c>
+      <c r="F4011" t="s">
+        <v>635</v>
+      </c>
+      <c r="G4011">
+        <v>335549</v>
+      </c>
+      <c r="H4011" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4012" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4012" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4012" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4012" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4012">
+        <v>6</v>
+      </c>
+      <c r="E4012">
+        <v>47.56</v>
+      </c>
+      <c r="F4012" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4012">
+        <v>336051</v>
+      </c>
+      <c r="H4012" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4013" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4013" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4013" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4013" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4013">
+        <v>6</v>
+      </c>
+      <c r="E4013">
+        <v>45.32</v>
+      </c>
+      <c r="F4013" t="s">
+        <v>946</v>
+      </c>
+      <c r="G4013">
+        <v>336052</v>
+      </c>
+      <c r="H4013" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4014" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4014" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4014" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4014">
+        <v>5</v>
+      </c>
+      <c r="E4014">
+        <v>38.22</v>
+      </c>
+      <c r="F4014" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4014">
+        <v>336053</v>
+      </c>
+      <c r="H4014" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4015" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4015" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4015" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4015" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4015">
+        <v>5</v>
+      </c>
+      <c r="E4015">
+        <v>40</v>
+      </c>
+      <c r="F4015" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4015">
+        <v>336054</v>
+      </c>
+      <c r="H4015" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4016" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4016" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4016" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4016">
+        <v>4</v>
+      </c>
+      <c r="E4016">
+        <v>30.14</v>
+      </c>
+      <c r="F4016" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4016">
+        <v>336055</v>
+      </c>
+      <c r="H4016" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4017" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4017" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4017" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4017">
+        <v>5</v>
+      </c>
+      <c r="E4017">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="F4017" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4017">
+        <v>335545</v>
+      </c>
+      <c r="H4017" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4018" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4018" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4018" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4018">
+        <v>6</v>
+      </c>
+      <c r="E4018">
+        <v>44.32</v>
+      </c>
+      <c r="F4018" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4018">
+        <v>335547</v>
+      </c>
+      <c r="H4018" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4019" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4019" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4019" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4019">
+        <v>6</v>
+      </c>
+      <c r="E4019">
+        <v>41.36</v>
+      </c>
+      <c r="F4019" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4019">
+        <v>335550</v>
+      </c>
+      <c r="H4019" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4020" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4020" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4020" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4020">
+        <v>5</v>
+      </c>
+      <c r="E4020">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F4020" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4020">
+        <v>335532</v>
+      </c>
+      <c r="H4020" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4021" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4021" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4021" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4021">
+        <v>5</v>
+      </c>
+      <c r="E4021">
+        <v>35.54</v>
+      </c>
+      <c r="F4021" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4021">
+        <v>335531</v>
+      </c>
+      <c r="H4021" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4022" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4022" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4022" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4022">
+        <v>5</v>
+      </c>
+      <c r="E4022">
+        <v>36.340000000000003</v>
+      </c>
+      <c r="F4022" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4022">
+        <v>335530</v>
+      </c>
+      <c r="H4022" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4023" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4023" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4023" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4023">
+        <v>5</v>
+      </c>
+      <c r="E4023">
+        <v>33.36</v>
+      </c>
+      <c r="F4023" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4023">
+        <v>335529</v>
+      </c>
+      <c r="H4023" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4024" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4024" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4024" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4024">
+        <v>3</v>
+      </c>
+      <c r="E4024">
+        <v>12.82</v>
+      </c>
+      <c r="F4024" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4024">
+        <v>334794</v>
+      </c>
+      <c r="H4024" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4025" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4025" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4025" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4025">
+        <v>3</v>
+      </c>
+      <c r="E4025">
+        <v>11.81</v>
+      </c>
+      <c r="F4025" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4025">
+        <v>334805</v>
+      </c>
+      <c r="H4025" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4026" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4026" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4026" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4026">
+        <v>2</v>
+      </c>
+      <c r="E4026">
+        <v>9.73</v>
+      </c>
+      <c r="F4026" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4026">
+        <v>334808</v>
+      </c>
+      <c r="H4026" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4027" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4027" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4027" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4027" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4027">
+        <v>2</v>
+      </c>
+      <c r="E4027">
+        <v>14.94</v>
+      </c>
+      <c r="F4027" t="s">
+        <v>722</v>
+      </c>
+      <c r="G4027">
+        <v>336061</v>
+      </c>
+      <c r="H4027" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4028" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4028" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4028" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4028" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4028">
+        <v>1</v>
+      </c>
+      <c r="E4028">
+        <v>14.38</v>
+      </c>
+      <c r="F4028" t="s">
+        <v>706</v>
+      </c>
+      <c r="G4028">
+        <v>336062</v>
+      </c>
+      <c r="H4028" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4029" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4029" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4029" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4029" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4029">
+        <v>6</v>
+      </c>
+      <c r="E4029">
+        <v>39.42</v>
+      </c>
+      <c r="F4029" t="s">
+        <v>635</v>
+      </c>
+      <c r="G4029">
+        <v>336056</v>
+      </c>
+      <c r="H4029" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4030" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4030" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4030" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4030" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4030">
+        <v>6</v>
+      </c>
+      <c r="E4030">
+        <v>44.56</v>
+      </c>
+      <c r="F4030" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4030">
+        <v>336057</v>
+      </c>
+      <c r="H4030" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4031" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4031" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4031" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4031" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4031">
+        <v>5</v>
+      </c>
+      <c r="E4031">
+        <v>30.2</v>
+      </c>
+      <c r="F4031" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4031">
+        <v>336058</v>
+      </c>
+      <c r="H4031" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4032" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4032" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4032" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4032">
+        <v>5</v>
+      </c>
+      <c r="E4032">
+        <v>34.74</v>
+      </c>
+      <c r="F4032" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4032">
+        <v>336059</v>
+      </c>
+      <c r="H4032" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4033" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4033" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4033" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4033" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4033">
+        <v>5</v>
+      </c>
+      <c r="E4033">
+        <v>33.58</v>
+      </c>
+      <c r="F4033" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4033">
+        <v>336060</v>
+      </c>
+      <c r="H4033" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4034" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4034" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4034" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4034" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4034">
+        <v>3</v>
+      </c>
+      <c r="E4034">
+        <v>11.06</v>
+      </c>
+      <c r="F4034" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4034">
+        <v>334861</v>
+      </c>
+      <c r="H4034" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4035" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4035" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4035" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4035" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4035">
+        <v>2</v>
+      </c>
+      <c r="E4035">
+        <v>12.01</v>
+      </c>
+      <c r="F4035" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4035">
+        <v>334858</v>
+      </c>
+      <c r="H4035" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4036" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4036" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4036" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4036" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4036">
+        <v>3</v>
+      </c>
+      <c r="E4036">
+        <v>12.08</v>
+      </c>
+      <c r="F4036" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4036">
+        <v>334871</v>
+      </c>
+      <c r="H4036" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4037" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4037" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4037" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4037" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4037">
+        <v>1</v>
+      </c>
+      <c r="E4037">
+        <v>10.18</v>
+      </c>
+      <c r="F4037" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4037">
+        <v>336065</v>
+      </c>
+      <c r="H4037" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4038" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4038" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4038" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4038" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4038">
+        <v>1</v>
+      </c>
+      <c r="E4038">
+        <v>7.94</v>
+      </c>
+      <c r="F4038" t="s">
+        <v>722</v>
+      </c>
+      <c r="G4038">
+        <v>336066</v>
+      </c>
+      <c r="H4038" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4039" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4039" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4039" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4039" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4039">
+        <v>1</v>
+      </c>
+      <c r="E4039">
+        <v>9.02</v>
+      </c>
+      <c r="F4039" t="s">
+        <v>706</v>
+      </c>
+      <c r="G4039">
+        <v>336064</v>
+      </c>
+      <c r="H4039" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4040" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4040" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4040" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4040" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4040">
+        <v>2</v>
+      </c>
+      <c r="E4040">
+        <v>14.38</v>
+      </c>
+      <c r="F4040" t="s">
+        <v>722</v>
+      </c>
+      <c r="G4040">
+        <v>336063</v>
+      </c>
+      <c r="H4040" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4041" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4041" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4041" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4041" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4041">
+        <v>6</v>
+      </c>
+      <c r="E4041">
+        <v>43.18</v>
+      </c>
+      <c r="F4041" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4041">
+        <v>336068</v>
+      </c>
+      <c r="H4041" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4042" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4042" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4042" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4042" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4042">
+        <v>5</v>
+      </c>
+      <c r="E4042">
+        <v>31.2</v>
+      </c>
+      <c r="F4042" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4042">
+        <v>336069</v>
+      </c>
+      <c r="H4042" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4043" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4043" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4043" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4043" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4043">
+        <v>6</v>
+      </c>
+      <c r="E4043">
+        <v>36.72</v>
+      </c>
+      <c r="F4043" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4043">
+        <v>336071</v>
+      </c>
+      <c r="H4043" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4044" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4044" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4044" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4044" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4044">
+        <v>6</v>
+      </c>
+      <c r="E4044">
+        <v>60.69</v>
+      </c>
+      <c r="F4044" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4044">
+        <v>336072</v>
+      </c>
+      <c r="H4044" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4045" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4045" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4045" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4045" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4045">
+        <v>6</v>
+      </c>
+      <c r="E4045">
+        <v>52.12</v>
+      </c>
+      <c r="F4045" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4045">
+        <v>336073</v>
+      </c>
+      <c r="H4045" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4046" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4046" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4046" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4046" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4046">
+        <v>4</v>
+      </c>
+      <c r="E4046">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="F4046" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4046">
+        <v>336074</v>
+      </c>
+      <c r="H4046" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4047" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4047" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4047" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4047" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4047">
+        <v>5</v>
+      </c>
+      <c r="E4047">
+        <v>41.12</v>
+      </c>
+      <c r="F4047" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4047">
+        <v>336075</v>
+      </c>
+      <c r="H4047" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4048" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4048" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4048" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4048" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4048">
+        <v>5</v>
+      </c>
+      <c r="E4048">
+        <v>38.58</v>
+      </c>
+      <c r="F4048" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4048">
+        <v>336076</v>
+      </c>
+      <c r="H4048" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4049" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4049" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4049" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4049" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4049">
+        <v>6</v>
+      </c>
+      <c r="E4049">
+        <v>43.62</v>
+      </c>
+      <c r="F4049" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4049">
+        <v>336077</v>
+      </c>
+      <c r="H4049" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4050" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4050" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4050" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4050" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4050">
+        <v>2</v>
+      </c>
+      <c r="E4050">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="F4050" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4050">
+        <v>334926</v>
+      </c>
+      <c r="H4050" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4051" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4051" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4051" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4051" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4051">
+        <v>1</v>
+      </c>
+      <c r="E4051">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F4051" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4051">
+        <v>336090</v>
+      </c>
+      <c r="H4051" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4052" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4052" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4052" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4052" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4052">
+        <v>4</v>
+      </c>
+      <c r="E4052">
+        <v>34.92</v>
+      </c>
+      <c r="F4052" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4052">
+        <v>336078</v>
+      </c>
+      <c r="H4052" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4053" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4053" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4053" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4053" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4053">
+        <v>5</v>
+      </c>
+      <c r="E4053">
+        <v>35.159999999999997</v>
+      </c>
+      <c r="F4053" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4053">
+        <v>336079</v>
+      </c>
+      <c r="H4053" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4054" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4054" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4054" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4054" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4054">
+        <v>5</v>
+      </c>
+      <c r="E4054">
+        <v>37.36</v>
+      </c>
+      <c r="F4054" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4054">
+        <v>336080</v>
+      </c>
+      <c r="H4054" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4055" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4055" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4055" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4055" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4055">
+        <v>1</v>
+      </c>
+      <c r="E4055">
+        <v>11.2</v>
+      </c>
+      <c r="F4055" t="s">
+        <v>722</v>
+      </c>
+      <c r="G4055">
+        <v>336089</v>
+      </c>
+      <c r="H4055" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4056" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4056" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4056" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4056" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4056">
+        <v>6</v>
+      </c>
+      <c r="E4056">
+        <v>43.76</v>
+      </c>
+      <c r="F4056" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4056">
+        <v>336081</v>
+      </c>
+      <c r="H4056" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4057" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4057" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4057" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4057" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4057">
+        <v>6</v>
+      </c>
+      <c r="E4057">
+        <v>45.92</v>
+      </c>
+      <c r="F4057" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4057">
+        <v>336082</v>
+      </c>
+      <c r="H4057" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4058" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4058" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4058" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4058" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4058">
+        <v>6</v>
+      </c>
+      <c r="E4058">
+        <v>53.16</v>
+      </c>
+      <c r="F4058" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4058">
+        <v>336083</v>
+      </c>
+      <c r="H4058" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4059" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4059" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4059" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4059" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4059">
+        <v>6</v>
+      </c>
+      <c r="E4059">
+        <v>58.52</v>
+      </c>
+      <c r="F4059" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4059">
+        <v>336084</v>
+      </c>
+      <c r="H4059" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4060" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4060" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4060" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4060">
+        <v>6</v>
+      </c>
+      <c r="E4060">
+        <v>52.26</v>
+      </c>
+      <c r="F4060" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4060">
+        <v>336085</v>
+      </c>
+      <c r="H4060" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4061" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4061" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4061" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4061">
+        <v>5</v>
+      </c>
+      <c r="E4061">
+        <v>44.78</v>
+      </c>
+      <c r="F4061" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4061">
+        <v>336086</v>
+      </c>
+      <c r="H4061" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4062" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4062" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4062" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4062">
+        <v>6</v>
+      </c>
+      <c r="E4062">
+        <v>52.42</v>
+      </c>
+      <c r="F4062" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4062">
+        <v>336087</v>
+      </c>
+      <c r="H4062" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4063" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4063" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4063" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4063">
+        <v>1</v>
+      </c>
+      <c r="E4063">
+        <v>14.1</v>
+      </c>
+      <c r="F4063" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4063">
+        <v>336088</v>
+      </c>
+      <c r="H4063" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4064" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4064" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4064" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4064">
+        <v>3</v>
+      </c>
+      <c r="E4064">
+        <v>12.68</v>
+      </c>
+      <c r="F4064" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4064">
+        <v>334928</v>
+      </c>
+      <c r="H4064" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4065" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4065" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4065" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4065">
+        <v>3</v>
+      </c>
+      <c r="E4065">
+        <v>8.74</v>
+      </c>
+      <c r="F4065" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4065">
+        <v>334936</v>
+      </c>
+      <c r="H4065" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4066" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4066" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4066" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4066">
+        <v>3</v>
+      </c>
+      <c r="E4066">
+        <v>15</v>
+      </c>
+      <c r="F4066" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4066">
+        <v>334976</v>
+      </c>
+      <c r="H4066" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4067" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4067" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4067" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4067">
+        <v>2</v>
+      </c>
+      <c r="E4067">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="F4067" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4067">
+        <v>334988</v>
+      </c>
+      <c r="H4067" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4068" t="s">
+        <v>949</v>
+      </c>
+      <c r="B4068" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4068" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4068">
+        <v>1</v>
+      </c>
+      <c r="E4068">
+        <v>4.92</v>
+      </c>
+      <c r="F4068" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4068">
+        <v>334984</v>
+      </c>
+      <c r="H4068" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4069" t="s">
+        <v>958</v>
+      </c>
+      <c r="B4069" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4069" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4069">
+        <v>2</v>
+      </c>
+      <c r="E4069">
+        <v>11.03</v>
+      </c>
+      <c r="F4069" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4069">
+        <v>335103</v>
+      </c>
+      <c r="H4069" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4070" t="s">
+        <v>959</v>
+      </c>
+      <c r="B4070" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4070" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4070">
+        <v>3</v>
+      </c>
+      <c r="E4070">
+        <v>11.62</v>
+      </c>
+      <c r="F4070" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4070">
+        <v>335116</v>
+      </c>
+      <c r="H4070" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4071" t="s">
+        <v>959</v>
+      </c>
+      <c r="B4071" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4071" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4071">
+        <v>3</v>
+      </c>
+      <c r="E4071">
+        <v>12.37</v>
+      </c>
+      <c r="F4071" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4071">
+        <v>335117</v>
+      </c>
+      <c r="H4071" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4072" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4072" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4072" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4072">
+        <v>2</v>
+      </c>
+      <c r="E4072">
+        <v>12.79</v>
+      </c>
+      <c r="F4072" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4072">
+        <v>335180</v>
+      </c>
+      <c r="H4072" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4073" t="s">
+        <v>950</v>
+      </c>
+      <c r="B4073" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4073" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4073">
+        <v>3</v>
+      </c>
+      <c r="E4073">
+        <v>15.02</v>
+      </c>
+      <c r="F4073" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4073">
+        <v>335212</v>
+      </c>
+      <c r="H4073" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4074" t="s">
+        <v>950</v>
+      </c>
+      <c r="B4074" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4074" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4074">
+        <v>3</v>
+      </c>
+      <c r="E4074">
+        <v>11.32</v>
+      </c>
+      <c r="F4074" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4074">
+        <v>335212</v>
+      </c>
+      <c r="H4074" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4075" t="s">
+        <v>950</v>
+      </c>
+      <c r="B4075" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4075" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4075">
+        <v>2</v>
+      </c>
+      <c r="E4075">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="F4075" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4075">
+        <v>335218</v>
+      </c>
+      <c r="H4075" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4076" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4076" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4076" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4076">
+        <v>5</v>
+      </c>
+      <c r="E4076">
+        <v>40.94</v>
+      </c>
+      <c r="F4076" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4076">
+        <v>336094</v>
+      </c>
+      <c r="H4076" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4077" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4077" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4077" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4077">
+        <v>5</v>
+      </c>
+      <c r="E4077">
+        <v>32</v>
+      </c>
+      <c r="F4077" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4077">
+        <v>336095</v>
+      </c>
+      <c r="H4077" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4078" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4078" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4078" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4078">
+        <v>6</v>
+      </c>
+      <c r="E4078">
+        <v>49.22</v>
+      </c>
+      <c r="F4078" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4078">
+        <v>336092</v>
+      </c>
+      <c r="H4078" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4079" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4079" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4079" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4079">
+        <v>6</v>
+      </c>
+      <c r="E4079">
+        <v>53.02</v>
+      </c>
+      <c r="F4079" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4079">
+        <v>336093</v>
+      </c>
+      <c r="H4079" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4080" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4080" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4080" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4080">
+        <v>6</v>
+      </c>
+      <c r="E4080">
+        <v>54.68</v>
+      </c>
+      <c r="F4080" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4080">
+        <v>336096</v>
+      </c>
+      <c r="H4080" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4081" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4081" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4081" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4081">
+        <v>6</v>
+      </c>
+      <c r="E4081">
+        <v>51.04</v>
+      </c>
+      <c r="F4081" t="s">
+        <v>635</v>
+      </c>
+      <c r="G4081">
+        <v>336706</v>
+      </c>
+      <c r="H4081" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4082" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4082" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4082" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4082">
+        <v>6</v>
+      </c>
+      <c r="E4082">
+        <v>54.38</v>
+      </c>
+      <c r="F4082" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4082">
+        <v>336707</v>
+      </c>
+      <c r="H4082" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4083" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4083" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4083" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4083">
+        <v>6</v>
+      </c>
+      <c r="E4083">
+        <v>48.88</v>
+      </c>
+      <c r="F4083" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4083">
+        <v>336709</v>
+      </c>
+      <c r="H4083" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4084" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4084" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4084" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4084">
+        <v>6</v>
+      </c>
+      <c r="E4084">
+        <v>49.68</v>
+      </c>
+      <c r="F4084" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4084">
+        <v>336710</v>
+      </c>
+      <c r="H4084" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4085" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4085" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4085" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4085">
+        <v>5</v>
+      </c>
+      <c r="E4085">
+        <v>43.14</v>
+      </c>
+      <c r="F4085" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4085">
+        <v>336711</v>
+      </c>
+      <c r="H4085" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4086" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4086" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4086" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4086">
+        <v>5</v>
+      </c>
+      <c r="E4086">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="F4086" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4086">
+        <v>336712</v>
+      </c>
+      <c r="H4086" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4087" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4087" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4087" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4087">
+        <v>5</v>
+      </c>
+      <c r="E4087">
+        <v>38.880000000000003</v>
+      </c>
+      <c r="F4087" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4087">
+        <v>336762</v>
+      </c>
+      <c r="H4087" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4088" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4088" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4088" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4088">
+        <v>6</v>
+      </c>
+      <c r="E4088">
+        <v>52.9</v>
+      </c>
+      <c r="F4088" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4088">
+        <v>336097</v>
+      </c>
+      <c r="H4088" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4089" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4089" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4089" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4089">
+        <v>6</v>
+      </c>
+      <c r="E4089">
+        <v>60.74</v>
+      </c>
+      <c r="F4089" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4089">
+        <v>336098</v>
+      </c>
+      <c r="H4089" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4090" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4090" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4090" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4090">
+        <v>6</v>
+      </c>
+      <c r="E4090">
+        <v>62.3</v>
+      </c>
+      <c r="F4090" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4090">
+        <v>336099</v>
+      </c>
+      <c r="H4090" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4091" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4091" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4091" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4091">
+        <v>6</v>
+      </c>
+      <c r="E4091">
+        <v>51.58</v>
+      </c>
+      <c r="F4091" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4091">
+        <v>336703</v>
+      </c>
+      <c r="H4091" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4092" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4092" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4092" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4092">
+        <v>6</v>
+      </c>
+      <c r="E4092">
+        <v>52.36</v>
+      </c>
+      <c r="F4092" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4092">
+        <v>336704</v>
+      </c>
+      <c r="H4092" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4093" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4093" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4093" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4093">
+        <v>6</v>
+      </c>
+      <c r="E4093">
+        <v>54.24</v>
+      </c>
+      <c r="F4093" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4093">
+        <v>336705</v>
+      </c>
+      <c r="H4093" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4094" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4094" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4094" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4094">
+        <v>6</v>
+      </c>
+      <c r="E4094">
+        <v>56.86</v>
+      </c>
+      <c r="F4094" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4094">
+        <v>336100</v>
+      </c>
+      <c r="H4094" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4095" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4095" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4095" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4095">
+        <v>6</v>
+      </c>
+      <c r="E4095">
+        <v>38.520000000000003</v>
+      </c>
+      <c r="F4095" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4095">
+        <v>336701</v>
+      </c>
+      <c r="H4095" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4096" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4096" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4096" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4096">
+        <v>6</v>
+      </c>
+      <c r="E4096">
+        <v>52.18</v>
+      </c>
+      <c r="F4096" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4096">
+        <v>336702</v>
+      </c>
+      <c r="H4096" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4097" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4097" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4097" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4097">
+        <v>6</v>
+      </c>
+      <c r="E4097">
+        <v>52.28</v>
+      </c>
+      <c r="F4097" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4097">
+        <v>336091</v>
+      </c>
+      <c r="H4097" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4098" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4098" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4098" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4098">
+        <v>3</v>
+      </c>
+      <c r="E4098">
+        <v>11.21</v>
+      </c>
+      <c r="F4098" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4098">
+        <v>335288</v>
+      </c>
+      <c r="H4098" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4099" t="s">
+        <v>951</v>
+      </c>
+      <c r="B4099" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4099" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4099">
+        <v>3</v>
+      </c>
+      <c r="E4099">
+        <v>11.51</v>
+      </c>
+      <c r="F4099" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4099">
+        <v>335318</v>
+      </c>
+      <c r="H4099" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4100" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4100" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4100" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4100">
+        <v>2</v>
+      </c>
+      <c r="E4100">
+        <v>10.85</v>
+      </c>
+      <c r="F4100" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4100">
+        <v>335325</v>
+      </c>
+      <c r="H4100" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4101" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4101" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4101" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4101">
+        <v>3</v>
+      </c>
+      <c r="E4101">
+        <v>14.5</v>
+      </c>
+      <c r="F4101" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4101">
+        <v>335667</v>
+      </c>
+      <c r="H4101" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4102" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4102" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4102" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4102">
+        <v>3</v>
+      </c>
+      <c r="E4102">
+        <v>12.02</v>
+      </c>
+      <c r="F4102" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4102">
+        <v>335288</v>
+      </c>
+      <c r="H4102" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4103" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4103" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4103" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4103">
+        <v>6</v>
+      </c>
+      <c r="E4103">
+        <v>48.22</v>
+      </c>
+      <c r="F4103" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4103">
+        <v>336717</v>
+      </c>
+      <c r="H4103" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4104" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4104" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4104" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4104">
+        <v>6</v>
+      </c>
+      <c r="E4104">
+        <v>50.5</v>
+      </c>
+      <c r="F4104" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4104">
+        <v>336718</v>
+      </c>
+      <c r="H4104" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4105" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4105" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4105" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4105">
+        <v>5</v>
+      </c>
+      <c r="E4105">
+        <v>39.24</v>
+      </c>
+      <c r="F4105" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4105">
+        <v>336719</v>
+      </c>
+      <c r="H4105" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4106" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4106" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4106" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4106">
+        <v>6</v>
+      </c>
+      <c r="E4106">
+        <v>36.68</v>
+      </c>
+      <c r="F4106" t="s">
+        <v>635</v>
+      </c>
+      <c r="G4106">
+        <v>336713</v>
+      </c>
+      <c r="H4106" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4107" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4107" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4107" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4107">
+        <v>5</v>
+      </c>
+      <c r="E4107">
+        <v>37.24</v>
+      </c>
+      <c r="F4107" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4107">
+        <v>336714</v>
+      </c>
+      <c r="H4107" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4108" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4108" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4108" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4108">
+        <v>5</v>
+      </c>
+      <c r="E4108">
+        <v>33.36</v>
+      </c>
+      <c r="F4108" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4108">
+        <v>336715</v>
+      </c>
+      <c r="H4108" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4109" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4109" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4109" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4109">
+        <v>3</v>
+      </c>
+      <c r="E4109">
+        <v>22.8</v>
+      </c>
+      <c r="F4109" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4109">
+        <v>336716</v>
+      </c>
+      <c r="H4109" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4110" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4110" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4110" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4110">
+        <v>3</v>
+      </c>
+      <c r="E4110">
+        <v>12.78</v>
+      </c>
+      <c r="F4110" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4110">
+        <v>335435</v>
+      </c>
+      <c r="H4110" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4111" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4111" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4111" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4111">
+        <v>1</v>
+      </c>
+      <c r="E4111">
+        <v>15.18</v>
+      </c>
+      <c r="F4111" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4111">
+        <v>336723</v>
+      </c>
+      <c r="H4111" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4112" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4112" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4112" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4112">
+        <v>1</v>
+      </c>
+      <c r="E4112">
+        <v>12.18</v>
+      </c>
+      <c r="F4112" t="s">
+        <v>954</v>
+      </c>
+      <c r="G4112">
+        <v>336722</v>
+      </c>
+      <c r="H4112" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4113" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4113" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4113" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4113">
+        <v>6</v>
+      </c>
+      <c r="E4113">
+        <v>48.72</v>
+      </c>
+      <c r="F4113" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4113">
+        <v>336720</v>
+      </c>
+      <c r="H4113" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4114" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4114" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4114" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4114" t="s">
+        <v>955</v>
+      </c>
+      <c r="E4114" t="s">
+        <v>956</v>
+      </c>
+      <c r="F4114" t="s">
+        <v>635</v>
+      </c>
+      <c r="G4114" t="s">
+        <v>957</v>
+      </c>
+      <c r="H4114" t="s">
         <v>899</v>
       </c>
     </row>

--- a/data/yield_data.xlsx
+++ b/data/yield_data.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19153" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19348" uniqueCount="967">
   <si>
     <t>Date</t>
   </si>
@@ -2871,6 +2871,15 @@
     <t>2026-06-28</t>
   </si>
   <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
     <t>2026-07-04</t>
   </si>
   <si>
@@ -2886,22 +2895,31 @@
     <t>AE002</t>
   </si>
   <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>53.08</t>
+    <t>51.42</t>
   </si>
   <si>
-    <t>336721</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
+    <t>336738</t>
   </si>
 </sst>
 </file>
@@ -3264,12 +3282,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4114"/>
+  <dimension ref="A1:H4151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -100402,7 +100418,7 @@
     </row>
     <row r="4069" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4069" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="B4069" t="s">
         <v>139</v>
@@ -100428,7 +100444,7 @@
     </row>
     <row r="4070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4070" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="B4070" t="s">
         <v>139</v>
@@ -100454,7 +100470,7 @@
     </row>
     <row r="4071" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4071" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="B4071" t="s">
         <v>139</v>
@@ -100480,7 +100496,7 @@
     </row>
     <row r="4072" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4072" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="B4072" t="s">
         <v>139</v>
@@ -100506,7 +100522,7 @@
     </row>
     <row r="4073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4073" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B4073" t="s">
         <v>139</v>
@@ -100532,7 +100548,7 @@
     </row>
     <row r="4074" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4074" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B4074" t="s">
         <v>139</v>
@@ -100558,7 +100574,7 @@
     </row>
     <row r="4075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4075" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B4075" t="s">
         <v>139</v>
@@ -100584,7 +100600,7 @@
     </row>
     <row r="4076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4076" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4076" t="s">
         <v>163</v>
@@ -100610,7 +100626,7 @@
     </row>
     <row r="4077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4077" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4077" t="s">
         <v>163</v>
@@ -100636,7 +100652,7 @@
     </row>
     <row r="4078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4078" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4078" t="s">
         <v>163</v>
@@ -100662,7 +100678,7 @@
     </row>
     <row r="4079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4079" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4079" t="s">
         <v>163</v>
@@ -100688,7 +100704,7 @@
     </row>
     <row r="4080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4080" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4080" t="s">
         <v>163</v>
@@ -100714,7 +100730,7 @@
     </row>
     <row r="4081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4081" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4081" t="s">
         <v>162</v>
@@ -100740,7 +100756,7 @@
     </row>
     <row r="4082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4082" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4082" t="s">
         <v>162</v>
@@ -100766,7 +100782,7 @@
     </row>
     <row r="4083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4083" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4083" t="s">
         <v>162</v>
@@ -100792,7 +100808,7 @@
     </row>
     <row r="4084" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4084" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4084" t="s">
         <v>162</v>
@@ -100818,7 +100834,7 @@
     </row>
     <row r="4085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4085" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4085" t="s">
         <v>162</v>
@@ -100844,7 +100860,7 @@
     </row>
     <row r="4086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4086" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4086" t="s">
         <v>162</v>
@@ -100870,7 +100886,7 @@
     </row>
     <row r="4087" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4087" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4087" t="s">
         <v>162</v>
@@ -100896,7 +100912,7 @@
     </row>
     <row r="4088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4088" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4088" t="s">
         <v>161</v>
@@ -100922,7 +100938,7 @@
     </row>
     <row r="4089" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4089" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4089" t="s">
         <v>161</v>
@@ -100948,7 +100964,7 @@
     </row>
     <row r="4090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4090" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4090" t="s">
         <v>161</v>
@@ -100974,7 +100990,7 @@
     </row>
     <row r="4091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4091" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4091" t="s">
         <v>161</v>
@@ -101000,7 +101016,7 @@
     </row>
     <row r="4092" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4092" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4092" t="s">
         <v>161</v>
@@ -101026,7 +101042,7 @@
     </row>
     <row r="4093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4093" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4093" t="s">
         <v>161</v>
@@ -101052,7 +101068,7 @@
     </row>
     <row r="4094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4094" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4094" t="s">
         <v>161</v>
@@ -101078,7 +101094,7 @@
     </row>
     <row r="4095" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4095" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4095" t="s">
         <v>164</v>
@@ -101104,7 +101120,7 @@
     </row>
     <row r="4096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4096" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4096" t="s">
         <v>164</v>
@@ -101130,7 +101146,7 @@
     </row>
     <row r="4097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4097" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4097" t="s">
         <v>164</v>
@@ -101156,7 +101172,7 @@
     </row>
     <row r="4098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4098" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4098" t="s">
         <v>139</v>
@@ -101182,7 +101198,7 @@
     </row>
     <row r="4099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4099" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B4099" t="s">
         <v>139</v>
@@ -101208,7 +101224,7 @@
     </row>
     <row r="4100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4100" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4100" t="s">
         <v>139</v>
@@ -101234,7 +101250,7 @@
     </row>
     <row r="4101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4101" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4101" t="s">
         <v>139</v>
@@ -101260,7 +101276,7 @@
     </row>
     <row r="4102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4102" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4102" t="s">
         <v>139</v>
@@ -101286,7 +101302,7 @@
     </row>
     <row r="4103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4103" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4103" t="s">
         <v>302</v>
@@ -101312,7 +101328,7 @@
     </row>
     <row r="4104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4104" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4104" t="s">
         <v>302</v>
@@ -101338,7 +101354,7 @@
     </row>
     <row r="4105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4105" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4105" t="s">
         <v>302</v>
@@ -101364,7 +101380,7 @@
     </row>
     <row r="4106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4106" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4106" t="s">
         <v>303</v>
@@ -101390,7 +101406,7 @@
     </row>
     <row r="4107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4107" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4107" t="s">
         <v>303</v>
@@ -101416,7 +101432,7 @@
     </row>
     <row r="4108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4108" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4108" t="s">
         <v>303</v>
@@ -101442,7 +101458,7 @@
     </row>
     <row r="4109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4109" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B4109" t="s">
         <v>303</v>
@@ -101468,7 +101484,7 @@
     </row>
     <row r="4110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4110" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B4110" t="s">
         <v>139</v>
@@ -101494,7 +101510,7 @@
     </row>
     <row r="4111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4111" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B4111" t="s">
         <v>163</v>
@@ -101520,7 +101536,7 @@
     </row>
     <row r="4112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4112" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B4112" t="s">
         <v>161</v>
@@ -101535,7 +101551,7 @@
         <v>12.18</v>
       </c>
       <c r="F4112" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="G4112">
         <v>336722</v>
@@ -101546,7 +101562,7 @@
     </row>
     <row r="4113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4113" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B4113" t="s">
         <v>302</v>
@@ -101572,7 +101588,7 @@
     </row>
     <row r="4114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4114" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B4114" t="s">
         <v>302</v>
@@ -101580,19 +101596,981 @@
       <c r="C4114" t="s">
         <v>228</v>
       </c>
-      <c r="D4114" t="s">
-        <v>955</v>
-      </c>
-      <c r="E4114" t="s">
-        <v>956</v>
+      <c r="D4114">
+        <v>6</v>
+      </c>
+      <c r="E4114">
+        <v>53.08</v>
       </c>
       <c r="F4114" t="s">
         <v>635</v>
       </c>
-      <c r="G4114" t="s">
-        <v>957</v>
+      <c r="G4114">
+        <v>336721</v>
       </c>
       <c r="H4114" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4115" t="s">
+        <v>958</v>
+      </c>
+      <c r="B4115" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4115">
+        <v>3</v>
+      </c>
+      <c r="E4115">
+        <v>15.19</v>
+      </c>
+      <c r="F4115" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4115">
+        <v>335445</v>
+      </c>
+      <c r="H4115" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4116" t="s">
+        <v>958</v>
+      </c>
+      <c r="B4116" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4116">
+        <v>2</v>
+      </c>
+      <c r="E4116">
+        <v>12.28</v>
+      </c>
+      <c r="F4116" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4116">
+        <v>335443</v>
+      </c>
+      <c r="H4116" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4117" t="s">
+        <v>958</v>
+      </c>
+      <c r="B4117" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4117">
+        <v>2</v>
+      </c>
+      <c r="E4117">
+        <v>12.44</v>
+      </c>
+      <c r="F4117" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4117">
+        <v>338504</v>
+      </c>
+      <c r="H4117" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4118" t="s">
+        <v>958</v>
+      </c>
+      <c r="B4118" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4118" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4118">
+        <v>2</v>
+      </c>
+      <c r="E4118">
+        <v>19.66</v>
+      </c>
+      <c r="F4118" t="s">
+        <v>907</v>
+      </c>
+      <c r="G4118">
+        <v>336724</v>
+      </c>
+      <c r="H4118" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4119" t="s">
+        <v>959</v>
+      </c>
+      <c r="B4119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4119" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4119">
+        <v>3</v>
+      </c>
+      <c r="E4119">
+        <v>13.91</v>
+      </c>
+      <c r="F4119" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4119">
+        <v>338576</v>
+      </c>
+      <c r="H4119" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4120" t="s">
+        <v>959</v>
+      </c>
+      <c r="B4120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4120" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4120">
+        <v>2</v>
+      </c>
+      <c r="E4120">
+        <v>10.79</v>
+      </c>
+      <c r="F4120" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4120">
+        <v>338575</v>
+      </c>
+      <c r="H4120" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4121" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4121" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4121">
+        <v>3</v>
+      </c>
+      <c r="E4121">
+        <v>12.52</v>
+      </c>
+      <c r="F4121" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4121">
+        <v>338629</v>
+      </c>
+      <c r="H4121" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4122" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4122" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4122">
+        <v>2</v>
+      </c>
+      <c r="E4122">
+        <v>10.8</v>
+      </c>
+      <c r="F4122" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4122">
+        <v>338643</v>
+      </c>
+      <c r="H4122" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4123" t="s">
+        <v>961</v>
+      </c>
+      <c r="B4123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4123" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4123">
+        <v>3</v>
+      </c>
+      <c r="E4123">
+        <v>12.54</v>
+      </c>
+      <c r="F4123" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4123">
+        <v>338723</v>
+      </c>
+      <c r="H4123" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4124" t="s">
+        <v>961</v>
+      </c>
+      <c r="B4124" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4124" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4124">
+        <v>3</v>
+      </c>
+      <c r="E4124">
+        <v>12.68</v>
+      </c>
+      <c r="F4124" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4124">
+        <v>338718</v>
+      </c>
+      <c r="H4124" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4125" t="s">
+        <v>961</v>
+      </c>
+      <c r="B4125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4125" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4125">
+        <v>2</v>
+      </c>
+      <c r="E4125">
+        <v>11.38</v>
+      </c>
+      <c r="F4125" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4125">
+        <v>338710</v>
+      </c>
+      <c r="H4125" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4126" t="s">
+        <v>962</v>
+      </c>
+      <c r="B4126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4126" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4126">
+        <v>3</v>
+      </c>
+      <c r="E4126">
+        <v>14.31</v>
+      </c>
+      <c r="F4126" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4126">
+        <v>399743</v>
+      </c>
+      <c r="H4126" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4127" t="s">
+        <v>962</v>
+      </c>
+      <c r="B4127" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4127" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4127">
+        <v>3</v>
+      </c>
+      <c r="E4127">
+        <v>12.4</v>
+      </c>
+      <c r="F4127" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4127">
+        <v>399901</v>
+      </c>
+      <c r="H4127" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4128" t="s">
+        <v>962</v>
+      </c>
+      <c r="B4128" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4128" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4128">
+        <v>2</v>
+      </c>
+      <c r="E4128">
+        <v>9.84</v>
+      </c>
+      <c r="F4128" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4128">
+        <v>399740</v>
+      </c>
+      <c r="H4128" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4129" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4129" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4129" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4129">
+        <v>3</v>
+      </c>
+      <c r="E4129">
+        <v>12.84</v>
+      </c>
+      <c r="F4129" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4129">
+        <v>401506</v>
+      </c>
+      <c r="H4129" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4130" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4130" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4130" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4130" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4130" t="s">
+        <v>965</v>
+      </c>
+      <c r="F4130" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4130" t="s">
+        <v>966</v>
+      </c>
+      <c r="H4130" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4131" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4131" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4131" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4131" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4131">
+        <v>60.32</v>
+      </c>
+      <c r="F4131" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4131">
+        <v>336740</v>
+      </c>
+      <c r="H4131" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4132" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4132" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4132" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4132" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4132">
+        <v>59.84</v>
+      </c>
+      <c r="F4132" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4132">
+        <v>336741</v>
+      </c>
+      <c r="H4132" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4133" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4133" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4133" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4133">
+        <v>49.12</v>
+      </c>
+      <c r="F4133" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4133">
+        <v>336742</v>
+      </c>
+      <c r="H4133" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4134" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4134" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4134" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4134" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4134">
+        <v>49.4</v>
+      </c>
+      <c r="F4134" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4134">
+        <v>336743</v>
+      </c>
+      <c r="H4134" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4135" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4135" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4135" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4135" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4135">
+        <v>61.32</v>
+      </c>
+      <c r="F4135" t="s">
+        <v>732</v>
+      </c>
+      <c r="G4135">
+        <v>336744</v>
+      </c>
+      <c r="H4135" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4136" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4136" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4136" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4136" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4136">
+        <v>42.58</v>
+      </c>
+      <c r="F4136" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4136">
+        <v>336745</v>
+      </c>
+      <c r="H4136" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4137" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4137" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4137" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4137" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4137">
+        <v>56.78</v>
+      </c>
+      <c r="F4137" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4137">
+        <v>336746</v>
+      </c>
+      <c r="H4137" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4138" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4138" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4138" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4138">
+        <v>5</v>
+      </c>
+      <c r="E4138">
+        <v>41.96</v>
+      </c>
+      <c r="F4138" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4138">
+        <v>337529</v>
+      </c>
+      <c r="H4138" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4139" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4139" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4139" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4139">
+        <v>6</v>
+      </c>
+      <c r="E4139">
+        <v>44.7</v>
+      </c>
+      <c r="F4139" t="s">
+        <v>730</v>
+      </c>
+      <c r="G4139">
+        <v>336732</v>
+      </c>
+      <c r="H4139" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4140" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4140" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4140" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4140">
+        <v>6</v>
+      </c>
+      <c r="E4140">
+        <v>48.7</v>
+      </c>
+      <c r="F4140" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4140">
+        <v>336735</v>
+      </c>
+      <c r="H4140" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4141" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4141" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4141" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4141">
+        <v>6</v>
+      </c>
+      <c r="E4141">
+        <v>44.68</v>
+      </c>
+      <c r="F4141" t="s">
+        <v>902</v>
+      </c>
+      <c r="G4141">
+        <v>336736</v>
+      </c>
+      <c r="H4141" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4142" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4142" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4142">
+        <v>6</v>
+      </c>
+      <c r="E4142">
+        <v>46.86</v>
+      </c>
+      <c r="F4142" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4142">
+        <v>336737</v>
+      </c>
+      <c r="H4142" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4143" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4143" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4143">
+        <v>5</v>
+      </c>
+      <c r="E4143">
+        <v>40.18</v>
+      </c>
+      <c r="F4143" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4143">
+        <v>336739</v>
+      </c>
+      <c r="H4143" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4144" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4144" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4144" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4144">
+        <v>49.42</v>
+      </c>
+      <c r="F4144" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4144">
+        <v>336729</v>
+      </c>
+      <c r="H4144" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4145" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4145" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4145" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4145">
+        <v>48.58</v>
+      </c>
+      <c r="F4145" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4145">
+        <v>336730</v>
+      </c>
+      <c r="H4145" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4146" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4146" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4146" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4146" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4146">
+        <v>51.76</v>
+      </c>
+      <c r="F4146" t="s">
+        <v>717</v>
+      </c>
+      <c r="G4146">
+        <v>336731</v>
+      </c>
+      <c r="H4146" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4147" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4147" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4147" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4147">
+        <v>5</v>
+      </c>
+      <c r="E4147">
+        <v>42.06</v>
+      </c>
+      <c r="F4147" t="s">
+        <v>731</v>
+      </c>
+      <c r="G4147">
+        <v>336734</v>
+      </c>
+      <c r="H4147" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4148" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4148" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4148">
+        <v>6</v>
+      </c>
+      <c r="E4148">
+        <v>54.58</v>
+      </c>
+      <c r="F4148" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4148">
+        <v>336726</v>
+      </c>
+      <c r="H4148" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4149" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4149" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4149">
+        <v>6</v>
+      </c>
+      <c r="E4149">
+        <v>52.22</v>
+      </c>
+      <c r="F4149" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4149">
+        <v>336727</v>
+      </c>
+      <c r="H4149" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4150" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4150" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4150" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4150">
+        <v>6</v>
+      </c>
+      <c r="E4150">
+        <v>56.7</v>
+      </c>
+      <c r="F4150" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4150">
+        <v>336728</v>
+      </c>
+      <c r="H4150" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4151" t="s">
+        <v>963</v>
+      </c>
+      <c r="B4151" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4151" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4151">
+        <v>4</v>
+      </c>
+      <c r="E4151">
+        <v>56.26</v>
+      </c>
+      <c r="F4151" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4151">
+        <v>336733</v>
+      </c>
+      <c r="H4151" t="s">
         <v>899</v>
       </c>
     </row>

--- a/data/yield_data.xlsx
+++ b/data/yield_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19348" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19478" uniqueCount="972">
   <si>
     <t>Date</t>
   </si>
@@ -2913,13 +2913,28 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>6</t>
+    <t>2026-07-14</t>
   </si>
   <si>
-    <t>51.42</t>
+    <t>MFR001</t>
   </si>
   <si>
-    <t>336738</t>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>403300</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
   </si>
 </sst>
 </file>
@@ -3282,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4151"/>
+  <dimension ref="A1:H4180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -102012,17 +102027,17 @@
       <c r="C4130" t="s">
         <v>228</v>
       </c>
-      <c r="D4130" t="s">
-        <v>964</v>
-      </c>
-      <c r="E4130" t="s">
-        <v>965</v>
+      <c r="D4130">
+        <v>6</v>
+      </c>
+      <c r="E4130">
+        <v>51.42</v>
       </c>
       <c r="F4130" t="s">
         <v>731</v>
       </c>
-      <c r="G4130" t="s">
-        <v>966</v>
+      <c r="G4130">
+        <v>336738</v>
       </c>
       <c r="H4130" t="s">
         <v>899</v>
@@ -102038,8 +102053,8 @@
       <c r="C4131" t="s">
         <v>228</v>
       </c>
-      <c r="D4131" t="s">
-        <v>964</v>
+      <c r="D4131">
+        <v>6</v>
       </c>
       <c r="E4131">
         <v>60.32</v>
@@ -102064,8 +102079,8 @@
       <c r="C4132" t="s">
         <v>228</v>
       </c>
-      <c r="D4132" t="s">
-        <v>964</v>
+      <c r="D4132">
+        <v>6</v>
       </c>
       <c r="E4132">
         <v>59.84</v>
@@ -102090,8 +102105,8 @@
       <c r="C4133" t="s">
         <v>228</v>
       </c>
-      <c r="D4133" t="s">
-        <v>964</v>
+      <c r="D4133">
+        <v>6</v>
       </c>
       <c r="E4133">
         <v>49.12</v>
@@ -102116,8 +102131,8 @@
       <c r="C4134" t="s">
         <v>228</v>
       </c>
-      <c r="D4134" t="s">
-        <v>964</v>
+      <c r="D4134">
+        <v>6</v>
       </c>
       <c r="E4134">
         <v>49.4</v>
@@ -102142,8 +102157,8 @@
       <c r="C4135" t="s">
         <v>228</v>
       </c>
-      <c r="D4135" t="s">
-        <v>964</v>
+      <c r="D4135">
+        <v>6</v>
       </c>
       <c r="E4135">
         <v>61.32</v>
@@ -102168,8 +102183,8 @@
       <c r="C4136" t="s">
         <v>228</v>
       </c>
-      <c r="D4136" t="s">
-        <v>964</v>
+      <c r="D4136">
+        <v>6</v>
       </c>
       <c r="E4136">
         <v>42.58</v>
@@ -102194,8 +102209,8 @@
       <c r="C4137" t="s">
         <v>228</v>
       </c>
-      <c r="D4137" t="s">
-        <v>964</v>
+      <c r="D4137">
+        <v>6</v>
       </c>
       <c r="E4137">
         <v>56.78</v>
@@ -102376,8 +102391,8 @@
       <c r="C4144" t="s">
         <v>228</v>
       </c>
-      <c r="D4144" t="s">
-        <v>964</v>
+      <c r="D4144">
+        <v>6</v>
       </c>
       <c r="E4144">
         <v>49.42</v>
@@ -102402,8 +102417,8 @@
       <c r="C4145" t="s">
         <v>228</v>
       </c>
-      <c r="D4145" t="s">
-        <v>964</v>
+      <c r="D4145">
+        <v>6</v>
       </c>
       <c r="E4145">
         <v>48.58</v>
@@ -102428,8 +102443,8 @@
       <c r="C4146" t="s">
         <v>228</v>
       </c>
-      <c r="D4146" t="s">
-        <v>964</v>
+      <c r="D4146">
+        <v>6</v>
       </c>
       <c r="E4146">
         <v>51.76</v>
@@ -102571,6 +102586,751 @@
         <v>336733</v>
       </c>
       <c r="H4151" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4152" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4152" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4152">
+        <v>1</v>
+      </c>
+      <c r="E4152">
+        <v>5.68</v>
+      </c>
+      <c r="F4152" t="s">
+        <v>965</v>
+      </c>
+      <c r="G4152">
+        <v>336748</v>
+      </c>
+      <c r="H4152" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4153" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4153" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4153" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4153">
+        <v>2</v>
+      </c>
+      <c r="E4153">
+        <v>15.68</v>
+      </c>
+      <c r="F4153" t="s">
+        <v>886</v>
+      </c>
+      <c r="G4153">
+        <v>336747</v>
+      </c>
+      <c r="H4153" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4154" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4154" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4154" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4154">
+        <v>3</v>
+      </c>
+      <c r="E4154">
+        <v>11.53</v>
+      </c>
+      <c r="F4154" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4154">
+        <v>402717</v>
+      </c>
+      <c r="H4154" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4155" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4155" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4155" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4155">
+        <v>2</v>
+      </c>
+      <c r="E4155">
+        <v>10.5</v>
+      </c>
+      <c r="F4155" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4155">
+        <v>402715</v>
+      </c>
+      <c r="H4155" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4156" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4156" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4156" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4156">
+        <v>3</v>
+      </c>
+      <c r="E4156">
+        <v>13.92</v>
+      </c>
+      <c r="F4156" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4156">
+        <v>402727</v>
+      </c>
+      <c r="H4156" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4157" t="s">
+        <v>966</v>
+      </c>
+      <c r="B4157" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4157" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4157">
+        <v>3</v>
+      </c>
+      <c r="E4157">
+        <v>12.01</v>
+      </c>
+      <c r="F4157" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4157">
+        <v>413764</v>
+      </c>
+      <c r="H4157" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4158" t="s">
+        <v>966</v>
+      </c>
+      <c r="B4158" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4158" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4158">
+        <v>3</v>
+      </c>
+      <c r="E4158">
+        <v>10.52</v>
+      </c>
+      <c r="F4158" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4158" t="s">
+        <v>967</v>
+      </c>
+      <c r="H4158" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4159" t="s">
+        <v>966</v>
+      </c>
+      <c r="B4159" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4159" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4159">
+        <v>2</v>
+      </c>
+      <c r="E4159">
+        <v>9.33</v>
+      </c>
+      <c r="F4159" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4159">
+        <v>413751</v>
+      </c>
+      <c r="H4159" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4160" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4160" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4160" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4160">
+        <v>2</v>
+      </c>
+      <c r="E4160">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="F4160" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4160">
+        <v>413829</v>
+      </c>
+      <c r="H4160" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4161" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4161" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4161" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4161">
+        <v>3</v>
+      </c>
+      <c r="E4161">
+        <v>13.72</v>
+      </c>
+      <c r="F4161" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4161">
+        <v>413838</v>
+      </c>
+      <c r="H4161" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4162" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4162" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4162" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4162">
+        <v>1</v>
+      </c>
+      <c r="E4162">
+        <v>19.96</v>
+      </c>
+      <c r="F4162" t="s">
+        <v>886</v>
+      </c>
+      <c r="G4162">
+        <v>337702</v>
+      </c>
+      <c r="H4162" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4163" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4163" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4163">
+        <v>1</v>
+      </c>
+      <c r="E4163">
+        <v>8.1</v>
+      </c>
+      <c r="F4163" t="s">
+        <v>965</v>
+      </c>
+      <c r="G4163">
+        <v>337703</v>
+      </c>
+      <c r="H4163" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4164" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4164" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4164" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4164">
+        <v>1</v>
+      </c>
+      <c r="E4164">
+        <v>19</v>
+      </c>
+      <c r="F4164" t="s">
+        <v>886</v>
+      </c>
+      <c r="G4164">
+        <v>337704</v>
+      </c>
+      <c r="H4164" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4165" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4165" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4165" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4165">
+        <v>1</v>
+      </c>
+      <c r="E4165">
+        <v>6.86</v>
+      </c>
+      <c r="F4165" t="s">
+        <v>706</v>
+      </c>
+      <c r="G4165">
+        <v>337705</v>
+      </c>
+      <c r="H4165" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4166" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4166" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4166" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4166">
+        <v>1</v>
+      </c>
+      <c r="E4166">
+        <v>11.54</v>
+      </c>
+      <c r="F4166" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4166">
+        <v>337706</v>
+      </c>
+      <c r="H4166" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4167" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4167" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4167" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4167">
+        <v>1</v>
+      </c>
+      <c r="E4167">
+        <v>12.52</v>
+      </c>
+      <c r="F4167" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4167">
+        <v>337701</v>
+      </c>
+      <c r="H4167" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4168" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4168" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4168" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4168">
+        <v>1</v>
+      </c>
+      <c r="E4168">
+        <v>12.24</v>
+      </c>
+      <c r="F4168" t="s">
+        <v>706</v>
+      </c>
+      <c r="G4168">
+        <v>336749</v>
+      </c>
+      <c r="H4168" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4169" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4169" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4169" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4169">
+        <v>1</v>
+      </c>
+      <c r="E4169">
+        <v>6.38</v>
+      </c>
+      <c r="F4169" t="s">
+        <v>965</v>
+      </c>
+      <c r="G4169">
+        <v>336750</v>
+      </c>
+      <c r="H4169" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4170" t="s">
+        <v>969</v>
+      </c>
+      <c r="B4170" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4170" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4170">
+        <v>3</v>
+      </c>
+      <c r="E4170">
+        <v>12.8</v>
+      </c>
+      <c r="F4170" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4170">
+        <v>413877</v>
+      </c>
+      <c r="H4170" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4171" t="s">
+        <v>969</v>
+      </c>
+      <c r="B4171" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4171" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4171">
+        <v>2</v>
+      </c>
+      <c r="E4171">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="F4171" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4171">
+        <v>413928</v>
+      </c>
+      <c r="H4171" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4172" t="s">
+        <v>969</v>
+      </c>
+      <c r="B4172" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4172" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4172">
+        <v>3</v>
+      </c>
+      <c r="E4172">
+        <v>13.47</v>
+      </c>
+      <c r="F4172" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4172">
+        <v>413930</v>
+      </c>
+      <c r="H4172" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4173" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4173" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4173" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4173">
+        <v>3</v>
+      </c>
+      <c r="E4173">
+        <v>12.47</v>
+      </c>
+      <c r="F4173" t="s">
+        <v>744</v>
+      </c>
+      <c r="G4173">
+        <v>413994</v>
+      </c>
+      <c r="H4173" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4174" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4174" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4174" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4174">
+        <v>3</v>
+      </c>
+      <c r="E4174">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="F4174" t="s">
+        <v>915</v>
+      </c>
+      <c r="G4174">
+        <v>414009</v>
+      </c>
+      <c r="H4174" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4175" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4175" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4175" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4175">
+        <v>6</v>
+      </c>
+      <c r="E4175">
+        <v>50.94</v>
+      </c>
+      <c r="F4175" t="s">
+        <v>734</v>
+      </c>
+      <c r="G4175">
+        <v>337708</v>
+      </c>
+      <c r="H4175" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4176" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4176" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4176" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4176">
+        <v>6</v>
+      </c>
+      <c r="E4176">
+        <v>48.82</v>
+      </c>
+      <c r="F4176" t="s">
+        <v>733</v>
+      </c>
+      <c r="G4176">
+        <v>337709</v>
+      </c>
+      <c r="H4176" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4177" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4177" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4177" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4177">
+        <v>6</v>
+      </c>
+      <c r="E4177">
+        <v>47.64</v>
+      </c>
+      <c r="G4177">
+        <v>337710</v>
+      </c>
+      <c r="H4177" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4178" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4178" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4178" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4178">
+        <v>6</v>
+      </c>
+      <c r="E4178">
+        <v>46.16</v>
+      </c>
+      <c r="G4178">
+        <v>337711</v>
+      </c>
+      <c r="H4178" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4179" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4179" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4179" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4179">
+        <v>6</v>
+      </c>
+      <c r="E4179">
+        <v>54.12</v>
+      </c>
+      <c r="G4179">
+        <v>337712</v>
+      </c>
+      <c r="H4179" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4180" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4180" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4180" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4180">
+        <v>5</v>
+      </c>
+      <c r="E4180">
+        <v>36.9</v>
+      </c>
+      <c r="F4180" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4180">
+        <v>337707</v>
+      </c>
+      <c r="H4180" t="s">
         <v>899</v>
       </c>
     </row>
